--- a/artfynd/A 59104-2025 artfynd.xlsx
+++ b/artfynd/A 59104-2025 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129996323</v>
+        <v>129996482</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>92887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435142</v>
+        <v>435094</v>
       </c>
       <c r="R2" t="n">
-        <v>6782181</v>
+        <v>6782249</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129996362</v>
+        <v>129996213</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>91569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,43 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434988</v>
+        <v>434850</v>
       </c>
       <c r="R3" t="n">
-        <v>6782383</v>
+        <v>6782509</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,6 +858,21 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -887,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129996328</v>
+        <v>129996423</v>
       </c>
       <c r="B4" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434942</v>
+        <v>434722</v>
       </c>
       <c r="R4" t="n">
-        <v>6782720</v>
+        <v>6782572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129996292</v>
+        <v>129996421</v>
       </c>
       <c r="B5" t="n">
-        <v>79677</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1019,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435018</v>
+        <v>434631</v>
       </c>
       <c r="R5" t="n">
-        <v>6782662</v>
+        <v>6782620</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1049,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129996344</v>
+        <v>129996445</v>
       </c>
       <c r="B6" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1116,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435157</v>
+        <v>435022</v>
       </c>
       <c r="R6" t="n">
-        <v>6782371</v>
+        <v>6782661</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,48 +1180,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129996482</v>
+        <v>129996281</v>
       </c>
       <c r="B7" t="n">
-        <v>92887</v>
+        <v>79706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435094</v>
+        <v>435132</v>
       </c>
       <c r="R7" t="n">
-        <v>6782249</v>
+        <v>6782205</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1259,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1279,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129996213</v>
+        <v>129996231</v>
       </c>
       <c r="B8" t="n">
-        <v>91569</v>
+        <v>79706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1314,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434850</v>
+        <v>434855</v>
       </c>
       <c r="R8" t="n">
-        <v>6782509</v>
+        <v>6782501</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,24 +1356,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1392,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129996281</v>
+        <v>129996426</v>
       </c>
       <c r="B9" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1427,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435132</v>
+        <v>434834</v>
       </c>
       <c r="R9" t="n">
-        <v>6782205</v>
+        <v>6782525</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1457,12 +1439,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129996231</v>
+        <v>129996420</v>
       </c>
       <c r="B10" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1500,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1524,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434855</v>
+        <v>434663</v>
       </c>
       <c r="R10" t="n">
-        <v>6782501</v>
+        <v>6782668</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129996483</v>
+        <v>129996435</v>
       </c>
       <c r="B11" t="n">
-        <v>78095</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1597,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1621,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434752</v>
+        <v>434970</v>
       </c>
       <c r="R11" t="n">
-        <v>6782544</v>
+        <v>6782543</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129996423</v>
+        <v>129996323</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1694,34 +1676,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434722</v>
+        <v>435142</v>
       </c>
       <c r="R12" t="n">
-        <v>6782572</v>
+        <v>6782181</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,12 +1738,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1780,45 +1770,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129996421</v>
+        <v>129996362</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434631</v>
+        <v>434988</v>
       </c>
       <c r="R13" t="n">
-        <v>6782620</v>
+        <v>6782383</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1845,12 +1844,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1859,6 +1858,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129996445</v>
+        <v>129996328</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1888,21 +1888,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435022</v>
+        <v>434942</v>
       </c>
       <c r="R14" t="n">
-        <v>6782661</v>
+        <v>6782720</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1974,10 +1974,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129996426</v>
+        <v>129996292</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1985,21 +1985,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434834</v>
+        <v>435018</v>
       </c>
       <c r="R15" t="n">
-        <v>6782525</v>
+        <v>6782662</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2071,10 +2071,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129996420</v>
+        <v>129996344</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2082,21 +2082,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434663</v>
+        <v>435157</v>
       </c>
       <c r="R16" t="n">
-        <v>6782668</v>
+        <v>6782371</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2136,12 +2136,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2168,10 +2168,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129996435</v>
+        <v>129996483</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>78095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434970</v>
+        <v>434752</v>
       </c>
       <c r="R17" t="n">
-        <v>6782543</v>
+        <v>6782544</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -6543,10 +6543,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129996449</v>
+        <v>129996377</v>
       </c>
       <c r="B61" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6554,21 +6554,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435085</v>
+        <v>435023</v>
       </c>
       <c r="R61" t="n">
-        <v>6782555</v>
+        <v>6782674</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6640,7 +6640,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129996404</v>
+        <v>129996449</v>
       </c>
       <c r="B62" t="n">
         <v>79087</v>
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>435071</v>
+        <v>435085</v>
       </c>
       <c r="R62" t="n">
-        <v>6782409</v>
+        <v>6782555</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6737,7 +6737,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129996468</v>
+        <v>129996404</v>
       </c>
       <c r="B63" t="n">
         <v>79087</v>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>435181</v>
+        <v>435071</v>
       </c>
       <c r="R63" t="n">
-        <v>6782175</v>
+        <v>6782409</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6834,10 +6834,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129996377</v>
+        <v>129996468</v>
       </c>
       <c r="B64" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6845,21 +6845,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>435023</v>
+        <v>435181</v>
       </c>
       <c r="R64" t="n">
-        <v>6782674</v>
+        <v>6782175</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8815,10 +8815,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129996255</v>
+        <v>129996439</v>
       </c>
       <c r="B84" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8826,21 +8826,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8850,10 +8850,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434998</v>
+        <v>435093</v>
       </c>
       <c r="R84" t="n">
-        <v>6782675</v>
+        <v>6782501</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8912,10 +8912,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129996229</v>
+        <v>129996406</v>
       </c>
       <c r="B85" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8923,21 +8923,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8947,10 +8947,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434658</v>
+        <v>434821</v>
       </c>
       <c r="R85" t="n">
-        <v>6782564</v>
+        <v>6782740</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9009,10 +9009,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129996253</v>
+        <v>129996462</v>
       </c>
       <c r="B86" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9020,21 +9020,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9044,10 +9044,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>435109</v>
+        <v>435151</v>
       </c>
       <c r="R86" t="n">
-        <v>6782484</v>
+        <v>6782374</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9106,10 +9106,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129996387</v>
+        <v>129996438</v>
       </c>
       <c r="B87" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9117,21 +9117,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9141,10 +9141,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>435183</v>
+        <v>435115</v>
       </c>
       <c r="R87" t="n">
-        <v>6782321</v>
+        <v>6782481</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9203,10 +9203,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129996230</v>
+        <v>129996352</v>
       </c>
       <c r="B88" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9214,21 +9214,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9238,10 +9238,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>434674</v>
+        <v>435089</v>
       </c>
       <c r="R88" t="n">
-        <v>6782596</v>
+        <v>6782304</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9268,12 +9268,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9300,10 +9300,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129996438</v>
+        <v>129996285</v>
       </c>
       <c r="B89" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9311,21 +9311,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9335,10 +9335,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>435115</v>
+        <v>434632</v>
       </c>
       <c r="R89" t="n">
-        <v>6782481</v>
+        <v>6782651</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9365,12 +9365,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9397,10 +9397,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129996439</v>
+        <v>129996337</v>
       </c>
       <c r="B90" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9408,21 +9408,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9432,10 +9432,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>435093</v>
+        <v>435057</v>
       </c>
       <c r="R90" t="n">
-        <v>6782501</v>
+        <v>6782494</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9494,10 +9494,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129996406</v>
+        <v>129996333</v>
       </c>
       <c r="B91" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9505,21 +9505,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9529,10 +9529,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>434821</v>
+        <v>434909</v>
       </c>
       <c r="R91" t="n">
-        <v>6782740</v>
+        <v>6782588</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9591,10 +9591,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129996462</v>
+        <v>129996255</v>
       </c>
       <c r="B92" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9602,21 +9602,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>435151</v>
+        <v>434998</v>
       </c>
       <c r="R92" t="n">
-        <v>6782374</v>
+        <v>6782675</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9688,10 +9688,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129996352</v>
+        <v>129996229</v>
       </c>
       <c r="B93" t="n">
-        <v>78845</v>
+        <v>79706</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9699,21 +9699,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9723,10 +9723,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>435089</v>
+        <v>434658</v>
       </c>
       <c r="R93" t="n">
-        <v>6782304</v>
+        <v>6782564</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9753,12 +9753,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9785,10 +9785,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129996285</v>
+        <v>129996253</v>
       </c>
       <c r="B94" t="n">
-        <v>79677</v>
+        <v>79706</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9796,21 +9796,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9820,10 +9820,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>434632</v>
+        <v>435109</v>
       </c>
       <c r="R94" t="n">
-        <v>6782651</v>
+        <v>6782484</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9850,12 +9850,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9882,10 +9882,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129996296</v>
+        <v>129996387</v>
       </c>
       <c r="B95" t="n">
-        <v>79677</v>
+        <v>78844</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9893,21 +9893,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>435156</v>
+        <v>435183</v>
       </c>
       <c r="R95" t="n">
-        <v>6782351</v>
+        <v>6782321</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9979,10 +9979,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129996337</v>
+        <v>129996230</v>
       </c>
       <c r="B96" t="n">
-        <v>78845</v>
+        <v>79706</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9990,21 +9990,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10014,10 +10014,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>435057</v>
+        <v>434674</v>
       </c>
       <c r="R96" t="n">
-        <v>6782494</v>
+        <v>6782596</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10044,12 +10044,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10076,10 +10076,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129996333</v>
+        <v>129996296</v>
       </c>
       <c r="B97" t="n">
-        <v>78845</v>
+        <v>79677</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10087,21 +10087,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10111,10 +10111,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>434909</v>
+        <v>435156</v>
       </c>
       <c r="R97" t="n">
-        <v>6782588</v>
+        <v>6782351</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10173,10 +10173,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129996446</v>
+        <v>129996338</v>
       </c>
       <c r="B98" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10184,21 +10184,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10208,10 +10208,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>435018</v>
+        <v>435074</v>
       </c>
       <c r="R98" t="n">
-        <v>6782668</v>
+        <v>6782438</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10270,45 +10270,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129996457</v>
+        <v>129996355</v>
       </c>
       <c r="B99" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>434993</v>
+        <v>434841</v>
       </c>
       <c r="R99" t="n">
-        <v>6782408</v>
+        <v>6782494</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10335,12 +10344,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10349,6 +10358,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10367,10 +10377,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129996249</v>
+        <v>129996446</v>
       </c>
       <c r="B100" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10378,21 +10388,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10402,10 +10412,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>434946</v>
+        <v>435018</v>
       </c>
       <c r="R100" t="n">
-        <v>6782584</v>
+        <v>6782668</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10432,12 +10442,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10464,10 +10474,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129996251</v>
+        <v>129996457</v>
       </c>
       <c r="B101" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10475,21 +10485,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10499,10 +10509,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>434956</v>
+        <v>434993</v>
       </c>
       <c r="R101" t="n">
-        <v>6782574</v>
+        <v>6782408</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10529,12 +10539,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10561,7 +10571,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129996237</v>
+        <v>129996249</v>
       </c>
       <c r="B102" t="n">
         <v>79706</v>
@@ -10596,10 +10606,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>434753</v>
+        <v>434946</v>
       </c>
       <c r="R102" t="n">
-        <v>6782550</v>
+        <v>6782584</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10658,7 +10668,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129996282</v>
+        <v>129996251</v>
       </c>
       <c r="B103" t="n">
         <v>79706</v>
@@ -10693,10 +10703,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>435143</v>
+        <v>434956</v>
       </c>
       <c r="R103" t="n">
-        <v>6782302</v>
+        <v>6782574</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10723,12 +10733,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10755,7 +10765,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129996257</v>
+        <v>129996237</v>
       </c>
       <c r="B104" t="n">
         <v>79706</v>
@@ -10790,10 +10800,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>435039</v>
+        <v>434753</v>
       </c>
       <c r="R104" t="n">
-        <v>6782675</v>
+        <v>6782550</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10820,12 +10830,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10852,10 +10862,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129996316</v>
+        <v>129996282</v>
       </c>
       <c r="B105" t="n">
-        <v>57737</v>
+        <v>79706</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10863,42 +10873,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>434898</v>
+        <v>435143</v>
       </c>
       <c r="R105" t="n">
-        <v>6782728</v>
+        <v>6782302</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10925,12 +10927,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10957,10 +10959,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129996338</v>
+        <v>129996257</v>
       </c>
       <c r="B106" t="n">
-        <v>78845</v>
+        <v>79706</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10968,21 +10970,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10992,10 +10994,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>435074</v>
+        <v>435039</v>
       </c>
       <c r="R106" t="n">
-        <v>6782438</v>
+        <v>6782675</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11054,41 +11056,40 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129996355</v>
+        <v>129996316</v>
       </c>
       <c r="B107" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -11098,10 +11099,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>434841</v>
+        <v>434898</v>
       </c>
       <c r="R107" t="n">
-        <v>6782494</v>
+        <v>6782728</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11142,7 +11143,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -12244,45 +12244,48 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129996348</v>
+        <v>129996481</v>
       </c>
       <c r="B119" t="n">
-        <v>78845</v>
+        <v>92887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>435230</v>
+        <v>434976</v>
       </c>
       <c r="R119" t="n">
-        <v>6782260</v>
+        <v>6782376</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12323,6 +12326,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12341,10 +12345,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129996342</v>
+        <v>129996447</v>
       </c>
       <c r="B120" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12352,21 +12356,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12376,10 +12380,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>435104</v>
+        <v>435039</v>
       </c>
       <c r="R120" t="n">
-        <v>6782300</v>
+        <v>6782658</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12438,10 +12442,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129996332</v>
+        <v>129996403</v>
       </c>
       <c r="B121" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12449,21 +12453,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12473,10 +12477,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>434796</v>
+        <v>435025</v>
       </c>
       <c r="R121" t="n">
-        <v>6782579</v>
+        <v>6782389</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12535,10 +12539,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129996334</v>
+        <v>129996271</v>
       </c>
       <c r="B122" t="n">
-        <v>78845</v>
+        <v>79706</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12546,37 +12550,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>434994</v>
+        <v>435189</v>
       </c>
       <c r="R122" t="n">
-        <v>6782543</v>
+        <v>6782244</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12603,12 +12604,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12617,7 +12618,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12636,10 +12636,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129996298</v>
+        <v>129996259</v>
       </c>
       <c r="B123" t="n">
-        <v>79677</v>
+        <v>79706</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12647,21 +12647,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12671,10 +12671,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>435213</v>
+        <v>435020</v>
       </c>
       <c r="R123" t="n">
-        <v>6782254</v>
+        <v>6782612</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12733,48 +12733,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129996481</v>
+        <v>129996348</v>
       </c>
       <c r="B124" t="n">
-        <v>92887</v>
+        <v>78845</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>434976</v>
+        <v>435230</v>
       </c>
       <c r="R124" t="n">
-        <v>6782376</v>
+        <v>6782260</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12815,7 +12812,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -12834,10 +12830,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129996447</v>
+        <v>129996342</v>
       </c>
       <c r="B125" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12845,21 +12841,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12869,10 +12865,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>435039</v>
+        <v>435104</v>
       </c>
       <c r="R125" t="n">
-        <v>6782658</v>
+        <v>6782300</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12931,10 +12927,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129996403</v>
+        <v>129996332</v>
       </c>
       <c r="B126" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12942,21 +12938,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12966,10 +12962,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>435025</v>
+        <v>434796</v>
       </c>
       <c r="R126" t="n">
-        <v>6782389</v>
+        <v>6782579</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13028,10 +13024,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129996259</v>
+        <v>129996334</v>
       </c>
       <c r="B127" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13039,34 +13035,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>435020</v>
+        <v>434994</v>
       </c>
       <c r="R127" t="n">
-        <v>6782612</v>
+        <v>6782543</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13093,12 +13092,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13107,6 +13106,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13125,10 +13125,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129996271</v>
+        <v>129996298</v>
       </c>
       <c r="B128" t="n">
-        <v>79706</v>
+        <v>79677</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13136,21 +13136,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13160,10 +13160,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>435189</v>
+        <v>435213</v>
       </c>
       <c r="R128" t="n">
-        <v>6782244</v>
+        <v>6782254</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13906,10 +13906,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129996239</v>
+        <v>129996453</v>
       </c>
       <c r="B136" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13917,21 +13917,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13941,10 +13941,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>434775</v>
+        <v>435011</v>
       </c>
       <c r="R136" t="n">
-        <v>6782566</v>
+        <v>6782456</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13971,12 +13971,17 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14003,10 +14008,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129996266</v>
+        <v>129996454</v>
       </c>
       <c r="B137" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14014,21 +14019,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14038,10 +14043,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>434994</v>
+        <v>435024</v>
       </c>
       <c r="R137" t="n">
-        <v>6782358</v>
+        <v>6782432</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14100,10 +14105,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129996270</v>
+        <v>129996405</v>
       </c>
       <c r="B138" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14111,21 +14116,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14135,10 +14140,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>435158</v>
+        <v>435097</v>
       </c>
       <c r="R138" t="n">
-        <v>6782353</v>
+        <v>6782414</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14165,12 +14170,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14197,10 +14202,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129996388</v>
+        <v>129996239</v>
       </c>
       <c r="B139" t="n">
-        <v>78844</v>
+        <v>79706</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14208,21 +14213,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14232,10 +14237,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>435210</v>
+        <v>434775</v>
       </c>
       <c r="R139" t="n">
-        <v>6782209</v>
+        <v>6782566</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14262,12 +14267,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14294,10 +14299,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129996369</v>
+        <v>129996266</v>
       </c>
       <c r="B140" t="n">
-        <v>78844</v>
+        <v>79706</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14305,21 +14310,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14329,10 +14334,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>434939</v>
+        <v>434994</v>
       </c>
       <c r="R140" t="n">
-        <v>6782721</v>
+        <v>6782358</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14359,12 +14364,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14391,10 +14396,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129996453</v>
+        <v>129996270</v>
       </c>
       <c r="B141" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14402,21 +14407,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14426,10 +14431,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>435011</v>
+        <v>435158</v>
       </c>
       <c r="R141" t="n">
-        <v>6782456</v>
+        <v>6782353</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14462,11 +14467,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14493,10 +14493,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129996454</v>
+        <v>129996388</v>
       </c>
       <c r="B142" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14504,21 +14504,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14528,10 +14528,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>435024</v>
+        <v>435210</v>
       </c>
       <c r="R142" t="n">
-        <v>6782432</v>
+        <v>6782209</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14590,10 +14590,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129996405</v>
+        <v>129996369</v>
       </c>
       <c r="B143" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14601,21 +14601,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14625,10 +14625,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>435097</v>
+        <v>434939</v>
       </c>
       <c r="R143" t="n">
-        <v>6782414</v>
+        <v>6782721</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14687,10 +14687,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129996289</v>
+        <v>129996458</v>
       </c>
       <c r="B144" t="n">
-        <v>79677</v>
+        <v>79087</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14698,21 +14698,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14722,10 +14722,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>434909</v>
+        <v>434987</v>
       </c>
       <c r="R144" t="n">
-        <v>6782588</v>
+        <v>6782372</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14752,12 +14752,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -14784,43 +14784,37 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129996361</v>
+        <v>129996412</v>
       </c>
       <c r="B145" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -14828,10 +14822,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>435003</v>
+        <v>434847</v>
       </c>
       <c r="R145" t="n">
-        <v>6782399</v>
+        <v>6782878</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14858,12 +14852,17 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -14891,7 +14890,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129996458</v>
+        <v>129996460</v>
       </c>
       <c r="B146" t="n">
         <v>79087</v>
@@ -14926,10 +14925,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>434987</v>
+        <v>435106</v>
       </c>
       <c r="R146" t="n">
-        <v>6782372</v>
+        <v>6782315</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14988,7 +14987,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129996412</v>
+        <v>129996411</v>
       </c>
       <c r="B147" t="n">
         <v>79087</v>
@@ -15017,19 +15016,16 @@
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>434847</v>
+        <v>434854</v>
       </c>
       <c r="R147" t="n">
-        <v>6782878</v>
+        <v>6782808</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15064,18 +15060,12 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -15094,10 +15084,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129996460</v>
+        <v>129996243</v>
       </c>
       <c r="B148" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15105,21 +15095,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15129,10 +15119,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>435106</v>
+        <v>434780</v>
       </c>
       <c r="R148" t="n">
-        <v>6782315</v>
+        <v>6782593</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15159,12 +15149,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15191,10 +15181,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129996411</v>
+        <v>129996381</v>
       </c>
       <c r="B149" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15202,21 +15192,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15226,10 +15216,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>434854</v>
+        <v>434974</v>
       </c>
       <c r="R149" t="n">
-        <v>6782808</v>
+        <v>6782389</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15256,12 +15246,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15288,45 +15278,54 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129996243</v>
+        <v>129996361</v>
       </c>
       <c r="B150" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>434780</v>
+        <v>435003</v>
       </c>
       <c r="R150" t="n">
-        <v>6782593</v>
+        <v>6782399</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15353,12 +15352,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15367,6 +15366,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15385,10 +15385,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129996381</v>
+        <v>129996289</v>
       </c>
       <c r="B151" t="n">
-        <v>78844</v>
+        <v>79677</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15396,21 +15396,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15420,10 +15420,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>434974</v>
+        <v>434909</v>
       </c>
       <c r="R151" t="n">
-        <v>6782389</v>
+        <v>6782588</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15450,12 +15450,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15587,10 +15587,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129996452</v>
+        <v>129996225</v>
       </c>
       <c r="B153" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15598,21 +15598,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15622,10 +15622,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>435052</v>
+        <v>434627</v>
       </c>
       <c r="R153" t="n">
-        <v>6782442</v>
+        <v>6782646</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15652,17 +15652,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -15689,10 +15684,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129996470</v>
+        <v>129996372</v>
       </c>
       <c r="B154" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15700,21 +15695,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15724,10 +15719,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>435154</v>
+        <v>434761</v>
       </c>
       <c r="R154" t="n">
-        <v>6782190</v>
+        <v>6782557</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15754,12 +15749,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -15786,10 +15781,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129996440</v>
+        <v>129996256</v>
       </c>
       <c r="B155" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15797,21 +15792,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15821,10 +15816,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>434996</v>
+        <v>435012</v>
       </c>
       <c r="R155" t="n">
-        <v>6782623</v>
+        <v>6782696</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -15883,10 +15878,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129996278</v>
+        <v>129996475</v>
       </c>
       <c r="B156" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15894,21 +15889,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15918,10 +15913,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>435146</v>
+        <v>435086</v>
       </c>
       <c r="R156" t="n">
-        <v>6782198</v>
+        <v>6782263</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16182,10 +16177,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129996225</v>
+        <v>129996351</v>
       </c>
       <c r="B159" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16193,21 +16188,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16217,10 +16212,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>434627</v>
+        <v>435130</v>
       </c>
       <c r="R159" t="n">
-        <v>6782646</v>
+        <v>6782185</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16247,12 +16242,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16279,10 +16274,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129996372</v>
+        <v>129996452</v>
       </c>
       <c r="B160" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16290,21 +16285,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16314,10 +16309,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>434761</v>
+        <v>435052</v>
       </c>
       <c r="R160" t="n">
-        <v>6782557</v>
+        <v>6782442</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16344,12 +16339,17 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16376,10 +16376,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129996256</v>
+        <v>129996470</v>
       </c>
       <c r="B161" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16387,21 +16387,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16411,10 +16411,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>435012</v>
+        <v>435154</v>
       </c>
       <c r="R161" t="n">
-        <v>6782696</v>
+        <v>6782190</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16473,7 +16473,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129996475</v>
+        <v>129996440</v>
       </c>
       <c r="B162" t="n">
         <v>79087</v>
@@ -16508,10 +16508,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>435086</v>
+        <v>434996</v>
       </c>
       <c r="R162" t="n">
-        <v>6782263</v>
+        <v>6782623</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16570,53 +16570,45 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129996304</v>
+        <v>129996278</v>
       </c>
       <c r="B163" t="n">
-        <v>56930</v>
+        <v>79706</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>435028</v>
+        <v>435146</v>
       </c>
       <c r="R163" t="n">
-        <v>6782608</v>
+        <v>6782198</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16675,45 +16667,53 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129996351</v>
+        <v>129996304</v>
       </c>
       <c r="B164" t="n">
-        <v>78845</v>
+        <v>56930</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>435130</v>
+        <v>435028</v>
       </c>
       <c r="R164" t="n">
-        <v>6782185</v>
+        <v>6782608</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17257,7 +17257,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129996409</v>
+        <v>129996417</v>
       </c>
       <c r="B170" t="n">
         <v>79087</v>
@@ -17292,10 +17292,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>434902</v>
+        <v>434721</v>
       </c>
       <c r="R170" t="n">
-        <v>6782760</v>
+        <v>6782708</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17354,45 +17354,54 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129996433</v>
+        <v>129996366</v>
       </c>
       <c r="B171" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>434947</v>
+        <v>435185</v>
       </c>
       <c r="R171" t="n">
-        <v>6782576</v>
+        <v>6782177</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17419,12 +17428,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -17433,6 +17442,7 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -17451,10 +17461,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129996417</v>
+        <v>129996343</v>
       </c>
       <c r="B172" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17462,21 +17472,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17486,10 +17496,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>434721</v>
+        <v>435133</v>
       </c>
       <c r="R172" t="n">
-        <v>6782708</v>
+        <v>6782359</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17516,12 +17526,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -17548,10 +17558,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129996248</v>
+        <v>129996409</v>
       </c>
       <c r="B173" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17559,21 +17569,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17583,10 +17593,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>434943</v>
+        <v>434902</v>
       </c>
       <c r="R173" t="n">
-        <v>6782573</v>
+        <v>6782760</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17645,54 +17655,45 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129996366</v>
+        <v>129996433</v>
       </c>
       <c r="B174" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>435185</v>
+        <v>434947</v>
       </c>
       <c r="R174" t="n">
-        <v>6782177</v>
+        <v>6782576</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17719,12 +17720,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -17733,7 +17734,6 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -17752,10 +17752,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129996343</v>
+        <v>129996248</v>
       </c>
       <c r="B175" t="n">
-        <v>78845</v>
+        <v>79706</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17763,21 +17763,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17787,10 +17787,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>435133</v>
+        <v>434943</v>
       </c>
       <c r="R175" t="n">
-        <v>6782359</v>
+        <v>6782573</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -17817,12 +17817,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD175" t="b">

--- a/artfynd/A 59104-2025 artfynd.xlsx
+++ b/artfynd/A 59104-2025 artfynd.xlsx
@@ -3138,10 +3138,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129996463</v>
+        <v>129996295</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3149,21 +3149,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435172</v>
+        <v>434994</v>
       </c>
       <c r="R27" t="n">
-        <v>6782321</v>
+        <v>6782360</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3235,45 +3235,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129996444</v>
+        <v>129996359</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435010</v>
+        <v>434911</v>
       </c>
       <c r="R28" t="n">
-        <v>6782685</v>
+        <v>6782571</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3300,12 +3309,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3314,6 +3323,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3332,45 +3342,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129996226</v>
+        <v>129996353</v>
       </c>
       <c r="B29" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434636</v>
+        <v>434838</v>
       </c>
       <c r="R29" t="n">
-        <v>6782611</v>
+        <v>6782905</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3411,6 +3430,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3429,10 +3449,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129996214</v>
+        <v>129996463</v>
       </c>
       <c r="B30" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3440,21 +3460,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3464,10 +3484,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435028</v>
+        <v>435172</v>
       </c>
       <c r="R30" t="n">
-        <v>6782399</v>
+        <v>6782321</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3494,12 +3514,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3526,10 +3546,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129996371</v>
+        <v>129996444</v>
       </c>
       <c r="B31" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3537,21 +3557,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3561,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434852</v>
+        <v>435010</v>
       </c>
       <c r="R31" t="n">
-        <v>6782499</v>
+        <v>6782685</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3591,12 +3611,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3930,54 +3950,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129996359</v>
+        <v>129996226</v>
       </c>
       <c r="B35" t="n">
-        <v>8451</v>
+        <v>79706</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434911</v>
+        <v>434636</v>
       </c>
       <c r="R35" t="n">
-        <v>6782571</v>
+        <v>6782611</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4018,7 +4029,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4037,54 +4047,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129996353</v>
+        <v>129996214</v>
       </c>
       <c r="B36" t="n">
-        <v>8451</v>
+        <v>79706</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>434838</v>
+        <v>435028</v>
       </c>
       <c r="R36" t="n">
-        <v>6782905</v>
+        <v>6782399</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4125,7 +4126,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4144,10 +4144,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129996295</v>
+        <v>129996371</v>
       </c>
       <c r="B37" t="n">
-        <v>79677</v>
+        <v>78844</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4155,21 +4155,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434994</v>
+        <v>434852</v>
       </c>
       <c r="R37" t="n">
-        <v>6782360</v>
+        <v>6782499</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -6931,54 +6931,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129996357</v>
+        <v>129996299</v>
       </c>
       <c r="B65" t="n">
-        <v>8451</v>
+        <v>79677</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434753</v>
+        <v>435150</v>
       </c>
       <c r="R65" t="n">
-        <v>6782547</v>
+        <v>6782170</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7005,12 +6996,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7019,7 +7010,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7038,7 +7028,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129996299</v>
+        <v>129996293</v>
       </c>
       <c r="B66" t="n">
         <v>79677</v>
@@ -7073,10 +7063,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>435150</v>
+        <v>435076</v>
       </c>
       <c r="R66" t="n">
-        <v>6782170</v>
+        <v>6782540</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7135,45 +7125,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129996293</v>
+        <v>129996357</v>
       </c>
       <c r="B67" t="n">
-        <v>79677</v>
+        <v>8451</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>435076</v>
+        <v>434753</v>
       </c>
       <c r="R67" t="n">
-        <v>6782540</v>
+        <v>6782547</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7200,12 +7199,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7214,6 +7213,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7232,10 +7232,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129996246</v>
+        <v>129996459</v>
       </c>
       <c r="B68" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7243,21 +7243,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7267,10 +7267,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434807</v>
+        <v>435125</v>
       </c>
       <c r="R68" t="n">
-        <v>6782563</v>
+        <v>6782293</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7329,7 +7329,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129996274</v>
+        <v>129996247</v>
       </c>
       <c r="B69" t="n">
         <v>79706</v>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435211</v>
+        <v>434888</v>
       </c>
       <c r="R69" t="n">
-        <v>6782225</v>
+        <v>6782580</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7426,10 +7426,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129996441</v>
+        <v>129996380</v>
       </c>
       <c r="B70" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7437,21 +7437,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434998</v>
+        <v>435050</v>
       </c>
       <c r="R70" t="n">
-        <v>6782688</v>
+        <v>6782431</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7523,10 +7523,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129996319</v>
+        <v>129996234</v>
       </c>
       <c r="B71" t="n">
-        <v>57737</v>
+        <v>79706</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7534,42 +7534,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>434790</v>
+        <v>434836</v>
       </c>
       <c r="R71" t="n">
-        <v>6782588</v>
+        <v>6782526</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7628,10 +7620,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129996346</v>
+        <v>129996383</v>
       </c>
       <c r="B72" t="n">
-        <v>78845</v>
+        <v>78844</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7639,21 +7631,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7663,10 +7655,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435183</v>
+        <v>435009</v>
       </c>
       <c r="R72" t="n">
-        <v>6782321</v>
+        <v>6782361</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7725,7 +7717,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129996459</v>
+        <v>129996441</v>
       </c>
       <c r="B73" t="n">
         <v>79087</v>
@@ -7760,10 +7752,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>435125</v>
+        <v>434998</v>
       </c>
       <c r="R73" t="n">
-        <v>6782293</v>
+        <v>6782688</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7822,45 +7814,54 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129996432</v>
+        <v>129996358</v>
       </c>
       <c r="B74" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>434914</v>
+        <v>434760</v>
       </c>
       <c r="R74" t="n">
-        <v>6782567</v>
+        <v>6782538</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7895,17 +7896,13 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7924,10 +7921,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129996472</v>
+        <v>129996346</v>
       </c>
       <c r="B75" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7935,21 +7932,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7959,10 +7956,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>435148</v>
+        <v>435183</v>
       </c>
       <c r="R75" t="n">
-        <v>6782237</v>
+        <v>6782321</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8021,7 +8018,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129996427</v>
+        <v>129996432</v>
       </c>
       <c r="B76" t="n">
         <v>79087</v>
@@ -8056,10 +8053,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434810</v>
+        <v>434914</v>
       </c>
       <c r="R76" t="n">
-        <v>6782537</v>
+        <v>6782567</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8092,6 +8089,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8118,10 +8120,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129996247</v>
+        <v>129996472</v>
       </c>
       <c r="B77" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8129,21 +8131,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8153,10 +8155,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434888</v>
+        <v>435148</v>
       </c>
       <c r="R77" t="n">
-        <v>6782580</v>
+        <v>6782237</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8183,12 +8185,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8215,10 +8217,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129996380</v>
+        <v>129996427</v>
       </c>
       <c r="B78" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8226,21 +8228,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8250,10 +8252,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>435050</v>
+        <v>434810</v>
       </c>
       <c r="R78" t="n">
-        <v>6782431</v>
+        <v>6782537</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8280,12 +8282,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8312,7 +8314,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129996234</v>
+        <v>129996246</v>
       </c>
       <c r="B79" t="n">
         <v>79706</v>
@@ -8347,10 +8349,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>434836</v>
+        <v>434807</v>
       </c>
       <c r="R79" t="n">
-        <v>6782526</v>
+        <v>6782563</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8409,10 +8411,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129996383</v>
+        <v>129996274</v>
       </c>
       <c r="B80" t="n">
-        <v>78844</v>
+        <v>79706</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8420,21 +8422,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8444,10 +8446,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435009</v>
+        <v>435211</v>
       </c>
       <c r="R80" t="n">
-        <v>6782361</v>
+        <v>6782225</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8506,32 +8508,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129996305</v>
+        <v>129996319</v>
       </c>
       <c r="B81" t="n">
-        <v>56930</v>
+        <v>57737</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8539,7 +8541,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -8549,10 +8551,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>434975</v>
+        <v>434790</v>
       </c>
       <c r="R81" t="n">
-        <v>6782364</v>
+        <v>6782588</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8579,12 +8581,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8611,10 +8613,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129996358</v>
+        <v>129996305</v>
       </c>
       <c r="B82" t="n">
-        <v>8451</v>
+        <v>56930</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8622,30 +8624,29 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -8655,10 +8656,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>434760</v>
+        <v>434975</v>
       </c>
       <c r="R82" t="n">
-        <v>6782538</v>
+        <v>6782364</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8685,12 +8686,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8699,7 +8700,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8815,10 +8815,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129996439</v>
+        <v>129996255</v>
       </c>
       <c r="B84" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8826,21 +8826,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8850,10 +8850,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>435093</v>
+        <v>434998</v>
       </c>
       <c r="R84" t="n">
-        <v>6782501</v>
+        <v>6782675</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8912,10 +8912,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129996406</v>
+        <v>129996229</v>
       </c>
       <c r="B85" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8923,21 +8923,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8947,10 +8947,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434821</v>
+        <v>434658</v>
       </c>
       <c r="R85" t="n">
-        <v>6782740</v>
+        <v>6782564</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9009,10 +9009,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129996462</v>
+        <v>129996253</v>
       </c>
       <c r="B86" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9020,21 +9020,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9044,10 +9044,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>435151</v>
+        <v>435109</v>
       </c>
       <c r="R86" t="n">
-        <v>6782374</v>
+        <v>6782484</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9106,10 +9106,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129996438</v>
+        <v>129996387</v>
       </c>
       <c r="B87" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9117,21 +9117,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9141,10 +9141,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>435115</v>
+        <v>435183</v>
       </c>
       <c r="R87" t="n">
-        <v>6782481</v>
+        <v>6782321</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9203,10 +9203,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129996352</v>
+        <v>129996230</v>
       </c>
       <c r="B88" t="n">
-        <v>78845</v>
+        <v>79706</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9214,21 +9214,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9238,10 +9238,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>435089</v>
+        <v>434674</v>
       </c>
       <c r="R88" t="n">
-        <v>6782304</v>
+        <v>6782596</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9268,12 +9268,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9300,10 +9300,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129996285</v>
+        <v>129996438</v>
       </c>
       <c r="B89" t="n">
-        <v>79677</v>
+        <v>79087</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9311,21 +9311,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9335,10 +9335,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>434632</v>
+        <v>435115</v>
       </c>
       <c r="R89" t="n">
-        <v>6782651</v>
+        <v>6782481</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9365,12 +9365,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9397,10 +9397,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129996337</v>
+        <v>129996439</v>
       </c>
       <c r="B90" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9408,21 +9408,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9432,10 +9432,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>435057</v>
+        <v>435093</v>
       </c>
       <c r="R90" t="n">
-        <v>6782494</v>
+        <v>6782501</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9494,10 +9494,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129996333</v>
+        <v>129996406</v>
       </c>
       <c r="B91" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9505,21 +9505,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9529,10 +9529,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>434909</v>
+        <v>434821</v>
       </c>
       <c r="R91" t="n">
-        <v>6782588</v>
+        <v>6782740</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9591,10 +9591,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129996255</v>
+        <v>129996462</v>
       </c>
       <c r="B92" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9602,21 +9602,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>434998</v>
+        <v>435151</v>
       </c>
       <c r="R92" t="n">
-        <v>6782675</v>
+        <v>6782374</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9688,10 +9688,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129996229</v>
+        <v>129996352</v>
       </c>
       <c r="B93" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9699,21 +9699,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9723,10 +9723,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>434658</v>
+        <v>435089</v>
       </c>
       <c r="R93" t="n">
-        <v>6782564</v>
+        <v>6782304</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9753,12 +9753,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9785,10 +9785,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129996253</v>
+        <v>129996285</v>
       </c>
       <c r="B94" t="n">
-        <v>79706</v>
+        <v>79677</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9796,21 +9796,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9820,10 +9820,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>435109</v>
+        <v>434632</v>
       </c>
       <c r="R94" t="n">
-        <v>6782484</v>
+        <v>6782651</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9850,12 +9850,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9882,10 +9882,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129996387</v>
+        <v>129996296</v>
       </c>
       <c r="B95" t="n">
-        <v>78844</v>
+        <v>79677</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9893,21 +9893,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>435183</v>
+        <v>435156</v>
       </c>
       <c r="R95" t="n">
-        <v>6782321</v>
+        <v>6782351</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9979,10 +9979,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129996230</v>
+        <v>129996337</v>
       </c>
       <c r="B96" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9990,21 +9990,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10014,10 +10014,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>434674</v>
+        <v>435057</v>
       </c>
       <c r="R96" t="n">
-        <v>6782596</v>
+        <v>6782494</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10044,12 +10044,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10076,10 +10076,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129996296</v>
+        <v>129996333</v>
       </c>
       <c r="B97" t="n">
-        <v>79677</v>
+        <v>78845</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10087,21 +10087,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10111,10 +10111,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>435156</v>
+        <v>434909</v>
       </c>
       <c r="R97" t="n">
-        <v>6782351</v>
+        <v>6782588</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10173,10 +10173,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129996338</v>
+        <v>129996446</v>
       </c>
       <c r="B98" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10184,21 +10184,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10208,10 +10208,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>435074</v>
+        <v>435018</v>
       </c>
       <c r="R98" t="n">
-        <v>6782438</v>
+        <v>6782668</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10270,54 +10270,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129996355</v>
+        <v>129996457</v>
       </c>
       <c r="B99" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>434841</v>
+        <v>434993</v>
       </c>
       <c r="R99" t="n">
-        <v>6782494</v>
+        <v>6782408</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10344,12 +10335,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10358,7 +10349,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10377,10 +10367,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129996446</v>
+        <v>129996251</v>
       </c>
       <c r="B100" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10388,21 +10378,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10412,10 +10402,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>435018</v>
+        <v>434956</v>
       </c>
       <c r="R100" t="n">
-        <v>6782668</v>
+        <v>6782574</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10442,12 +10432,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10474,10 +10464,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129996457</v>
+        <v>129996237</v>
       </c>
       <c r="B101" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10485,21 +10475,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10509,10 +10499,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>434993</v>
+        <v>434753</v>
       </c>
       <c r="R101" t="n">
-        <v>6782408</v>
+        <v>6782550</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10539,12 +10529,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10571,45 +10561,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129996249</v>
+        <v>129996355</v>
       </c>
       <c r="B102" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>434946</v>
+        <v>434841</v>
       </c>
       <c r="R102" t="n">
-        <v>6782584</v>
+        <v>6782494</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10650,6 +10649,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10668,10 +10668,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129996251</v>
+        <v>129996338</v>
       </c>
       <c r="B103" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10679,21 +10679,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10703,10 +10703,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>434956</v>
+        <v>435074</v>
       </c>
       <c r="R103" t="n">
-        <v>6782574</v>
+        <v>6782438</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10733,12 +10733,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10765,7 +10765,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129996237</v>
+        <v>129996249</v>
       </c>
       <c r="B104" t="n">
         <v>79706</v>
@@ -10800,10 +10800,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>434753</v>
+        <v>434946</v>
       </c>
       <c r="R104" t="n">
-        <v>6782550</v>
+        <v>6782584</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11161,10 +11161,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129996466</v>
+        <v>129996291</v>
       </c>
       <c r="B108" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11172,21 +11172,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11196,10 +11196,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>435216</v>
+        <v>435034</v>
       </c>
       <c r="R108" t="n">
-        <v>6782197</v>
+        <v>6782669</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11258,7 +11258,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129996430</v>
+        <v>129996466</v>
       </c>
       <c r="B109" t="n">
         <v>79087</v>
@@ -11293,10 +11293,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>434828</v>
+        <v>435216</v>
       </c>
       <c r="R109" t="n">
-        <v>6782576</v>
+        <v>6782197</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11323,12 +11323,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11355,7 +11355,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129996448</v>
+        <v>129996430</v>
       </c>
       <c r="B110" t="n">
         <v>79087</v>
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>435054</v>
+        <v>434828</v>
       </c>
       <c r="R110" t="n">
-        <v>6782627</v>
+        <v>6782576</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11420,12 +11420,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11452,10 +11452,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129996280</v>
+        <v>129996448</v>
       </c>
       <c r="B111" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11463,21 +11463,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11487,10 +11487,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>435121</v>
+        <v>435054</v>
       </c>
       <c r="R111" t="n">
-        <v>6782201</v>
+        <v>6782627</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11937,10 +11937,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129996321</v>
+        <v>129996280</v>
       </c>
       <c r="B116" t="n">
-        <v>57737</v>
+        <v>79706</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11948,42 +11948,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>434990</v>
+        <v>435121</v>
       </c>
       <c r="R116" t="n">
-        <v>6782383</v>
+        <v>6782201</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12042,27 +12034,27 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129996326</v>
+        <v>129996321</v>
       </c>
       <c r="B117" t="n">
-        <v>56933</v>
+        <v>57737</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12075,7 +12067,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -12085,10 +12077,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>434930</v>
+        <v>434990</v>
       </c>
       <c r="R117" t="n">
-        <v>6782560</v>
+        <v>6782383</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12115,12 +12107,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12147,45 +12139,53 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129996291</v>
+        <v>129996326</v>
       </c>
       <c r="B118" t="n">
-        <v>79677</v>
+        <v>56933</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>229821</v>
+        <v>102613</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>435034</v>
+        <v>434930</v>
       </c>
       <c r="R118" t="n">
-        <v>6782669</v>
+        <v>6782560</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12212,12 +12212,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13324,10 +13324,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129996331</v>
+        <v>129996279</v>
       </c>
       <c r="B130" t="n">
-        <v>78845</v>
+        <v>79706</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13335,21 +13335,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13359,10 +13359,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>434773</v>
+        <v>435130</v>
       </c>
       <c r="R130" t="n">
-        <v>6782567</v>
+        <v>6782186</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13389,12 +13389,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13421,7 +13421,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129996279</v>
+        <v>129996240</v>
       </c>
       <c r="B131" t="n">
         <v>79706</v>
@@ -13456,10 +13456,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>435130</v>
+        <v>434765</v>
       </c>
       <c r="R131" t="n">
-        <v>6782186</v>
+        <v>6782566</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13486,12 +13486,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13518,10 +13518,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129996240</v>
+        <v>129996370</v>
       </c>
       <c r="B132" t="n">
-        <v>79706</v>
+        <v>78844</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13529,21 +13529,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>434765</v>
+        <v>434902</v>
       </c>
       <c r="R132" t="n">
-        <v>6782566</v>
+        <v>6782754</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13615,10 +13615,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129996370</v>
+        <v>129996238</v>
       </c>
       <c r="B133" t="n">
-        <v>78844</v>
+        <v>79706</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13626,21 +13626,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13650,10 +13650,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>434902</v>
+        <v>434763</v>
       </c>
       <c r="R133" t="n">
-        <v>6782754</v>
+        <v>6782555</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13712,7 +13712,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129996238</v>
+        <v>129996215</v>
       </c>
       <c r="B134" t="n">
         <v>79706</v>
@@ -13747,10 +13747,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>434763</v>
+        <v>434939</v>
       </c>
       <c r="R134" t="n">
-        <v>6782555</v>
+        <v>6782693</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13809,10 +13809,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129996215</v>
+        <v>129996331</v>
       </c>
       <c r="B135" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13820,21 +13820,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13844,10 +13844,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>434939</v>
+        <v>434773</v>
       </c>
       <c r="R135" t="n">
-        <v>6782693</v>
+        <v>6782567</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13906,10 +13906,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129996453</v>
+        <v>129996239</v>
       </c>
       <c r="B136" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13917,21 +13917,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13941,10 +13941,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>435011</v>
+        <v>434775</v>
       </c>
       <c r="R136" t="n">
-        <v>6782456</v>
+        <v>6782566</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13971,17 +13971,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14008,10 +14003,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129996454</v>
+        <v>129996266</v>
       </c>
       <c r="B137" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14019,21 +14014,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14043,10 +14038,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>435024</v>
+        <v>434994</v>
       </c>
       <c r="R137" t="n">
-        <v>6782432</v>
+        <v>6782358</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14105,10 +14100,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129996405</v>
+        <v>129996270</v>
       </c>
       <c r="B138" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14116,21 +14111,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14140,10 +14135,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>435097</v>
+        <v>435158</v>
       </c>
       <c r="R138" t="n">
-        <v>6782414</v>
+        <v>6782353</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14170,12 +14165,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14202,10 +14197,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129996239</v>
+        <v>129996388</v>
       </c>
       <c r="B139" t="n">
-        <v>79706</v>
+        <v>78844</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14213,21 +14208,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14237,10 +14232,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>434775</v>
+        <v>435210</v>
       </c>
       <c r="R139" t="n">
-        <v>6782566</v>
+        <v>6782209</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14267,12 +14262,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14299,10 +14294,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129996266</v>
+        <v>129996369</v>
       </c>
       <c r="B140" t="n">
-        <v>79706</v>
+        <v>78844</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14310,21 +14305,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14334,10 +14329,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>434994</v>
+        <v>434939</v>
       </c>
       <c r="R140" t="n">
-        <v>6782358</v>
+        <v>6782721</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14364,12 +14359,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14396,10 +14391,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129996270</v>
+        <v>129996453</v>
       </c>
       <c r="B141" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14407,21 +14402,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14431,10 +14426,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>435158</v>
+        <v>435011</v>
       </c>
       <c r="R141" t="n">
-        <v>6782353</v>
+        <v>6782456</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14467,6 +14462,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14493,10 +14493,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129996388</v>
+        <v>129996454</v>
       </c>
       <c r="B142" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14504,21 +14504,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14528,10 +14528,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>435210</v>
+        <v>435024</v>
       </c>
       <c r="R142" t="n">
-        <v>6782209</v>
+        <v>6782432</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14590,10 +14590,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129996369</v>
+        <v>129996405</v>
       </c>
       <c r="B143" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14601,21 +14601,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14625,10 +14625,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>434939</v>
+        <v>435097</v>
       </c>
       <c r="R143" t="n">
-        <v>6782721</v>
+        <v>6782414</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14687,10 +14687,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129996458</v>
+        <v>129996289</v>
       </c>
       <c r="B144" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14698,21 +14698,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14722,10 +14722,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>434987</v>
+        <v>434909</v>
       </c>
       <c r="R144" t="n">
-        <v>6782372</v>
+        <v>6782588</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14752,12 +14752,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -14784,37 +14784,43 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129996412</v>
+        <v>129996361</v>
       </c>
       <c r="B145" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -14822,10 +14828,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>434847</v>
+        <v>435003</v>
       </c>
       <c r="R145" t="n">
-        <v>6782878</v>
+        <v>6782399</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14852,17 +14858,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -14890,7 +14891,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129996460</v>
+        <v>129996458</v>
       </c>
       <c r="B146" t="n">
         <v>79087</v>
@@ -14925,10 +14926,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>435106</v>
+        <v>434987</v>
       </c>
       <c r="R146" t="n">
-        <v>6782315</v>
+        <v>6782372</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14987,7 +14988,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129996411</v>
+        <v>129996412</v>
       </c>
       <c r="B147" t="n">
         <v>79087</v>
@@ -15016,16 +15017,19 @@
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>434854</v>
+        <v>434847</v>
       </c>
       <c r="R147" t="n">
-        <v>6782808</v>
+        <v>6782878</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15060,12 +15064,18 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -15084,10 +15094,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129996243</v>
+        <v>129996460</v>
       </c>
       <c r="B148" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15095,21 +15105,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15119,10 +15129,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>434780</v>
+        <v>435106</v>
       </c>
       <c r="R148" t="n">
-        <v>6782593</v>
+        <v>6782315</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15149,12 +15159,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15181,10 +15191,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129996381</v>
+        <v>129996411</v>
       </c>
       <c r="B149" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15192,21 +15202,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15216,10 +15226,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>434974</v>
+        <v>434854</v>
       </c>
       <c r="R149" t="n">
-        <v>6782389</v>
+        <v>6782808</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15246,12 +15256,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15278,54 +15288,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129996361</v>
+        <v>129996243</v>
       </c>
       <c r="B150" t="n">
-        <v>8451</v>
+        <v>79706</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>435003</v>
+        <v>434780</v>
       </c>
       <c r="R150" t="n">
-        <v>6782399</v>
+        <v>6782593</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15352,12 +15353,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15366,7 +15367,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15385,10 +15385,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129996289</v>
+        <v>129996381</v>
       </c>
       <c r="B151" t="n">
-        <v>79677</v>
+        <v>78844</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15396,21 +15396,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15420,10 +15420,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>434909</v>
+        <v>434974</v>
       </c>
       <c r="R151" t="n">
-        <v>6782588</v>
+        <v>6782389</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15450,12 +15450,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15587,10 +15587,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129996225</v>
+        <v>129996452</v>
       </c>
       <c r="B153" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15598,21 +15598,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15622,10 +15622,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>434627</v>
+        <v>435052</v>
       </c>
       <c r="R153" t="n">
-        <v>6782646</v>
+        <v>6782442</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15652,12 +15652,17 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -15684,10 +15689,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129996372</v>
+        <v>129996470</v>
       </c>
       <c r="B154" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15695,21 +15700,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15719,10 +15724,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>434761</v>
+        <v>435154</v>
       </c>
       <c r="R154" t="n">
-        <v>6782557</v>
+        <v>6782190</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15749,12 +15754,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -15781,10 +15786,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129996256</v>
+        <v>129996440</v>
       </c>
       <c r="B155" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15792,21 +15797,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15816,10 +15821,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>435012</v>
+        <v>434996</v>
       </c>
       <c r="R155" t="n">
-        <v>6782696</v>
+        <v>6782623</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -15878,10 +15883,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129996475</v>
+        <v>129996278</v>
       </c>
       <c r="B156" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15889,21 +15894,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15913,10 +15918,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>435086</v>
+        <v>435146</v>
       </c>
       <c r="R156" t="n">
-        <v>6782263</v>
+        <v>6782198</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16177,10 +16182,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129996351</v>
+        <v>129996225</v>
       </c>
       <c r="B159" t="n">
-        <v>78845</v>
+        <v>79706</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16188,21 +16193,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16212,10 +16217,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>435130</v>
+        <v>434627</v>
       </c>
       <c r="R159" t="n">
-        <v>6782185</v>
+        <v>6782646</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16242,12 +16247,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16274,10 +16279,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129996452</v>
+        <v>129996372</v>
       </c>
       <c r="B160" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16285,21 +16290,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16309,10 +16314,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>435052</v>
+        <v>434761</v>
       </c>
       <c r="R160" t="n">
-        <v>6782442</v>
+        <v>6782557</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16339,17 +16344,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16376,10 +16376,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129996470</v>
+        <v>129996256</v>
       </c>
       <c r="B161" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16387,21 +16387,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16411,10 +16411,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>435154</v>
+        <v>435012</v>
       </c>
       <c r="R161" t="n">
-        <v>6782190</v>
+        <v>6782696</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16473,7 +16473,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129996440</v>
+        <v>129996475</v>
       </c>
       <c r="B162" t="n">
         <v>79087</v>
@@ -16508,10 +16508,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>434996</v>
+        <v>435086</v>
       </c>
       <c r="R162" t="n">
-        <v>6782623</v>
+        <v>6782263</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16570,45 +16570,53 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129996278</v>
+        <v>129996304</v>
       </c>
       <c r="B163" t="n">
-        <v>79706</v>
+        <v>56930</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>435146</v>
+        <v>435028</v>
       </c>
       <c r="R163" t="n">
-        <v>6782198</v>
+        <v>6782608</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16667,53 +16675,45 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129996304</v>
+        <v>129996351</v>
       </c>
       <c r="B164" t="n">
-        <v>56930</v>
+        <v>78845</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>435028</v>
+        <v>435130</v>
       </c>
       <c r="R164" t="n">
-        <v>6782608</v>
+        <v>6782185</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19423,10 +19423,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129996244</v>
+        <v>129996376</v>
       </c>
       <c r="B192" t="n">
-        <v>79706</v>
+        <v>78844</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19434,21 +19434,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19458,10 +19458,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>434789</v>
+        <v>435039</v>
       </c>
       <c r="R192" t="n">
-        <v>6782590</v>
+        <v>6782675</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19488,12 +19488,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -19520,7 +19520,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129996216</v>
+        <v>129996263</v>
       </c>
       <c r="B193" t="n">
         <v>79706</v>
@@ -19555,10 +19555,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>434928</v>
+        <v>435076</v>
       </c>
       <c r="R193" t="n">
-        <v>6782707</v>
+        <v>6782532</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19585,12 +19585,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -19617,10 +19617,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129996413</v>
+        <v>129996268</v>
       </c>
       <c r="B194" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19628,21 +19628,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19652,10 +19652,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>434840</v>
+        <v>435103</v>
       </c>
       <c r="R194" t="n">
-        <v>6782902</v>
+        <v>6782305</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19682,12 +19682,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -19714,7 +19714,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129996464</v>
+        <v>129996413</v>
       </c>
       <c r="B195" t="n">
         <v>79087</v>
@@ -19743,19 +19743,16 @@
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>435236</v>
+        <v>434840</v>
       </c>
       <c r="R195" t="n">
-        <v>6782220</v>
+        <v>6782902</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -19782,12 +19779,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -19796,7 +19793,6 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -19815,7 +19811,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129996425</v>
+        <v>129996464</v>
       </c>
       <c r="B196" t="n">
         <v>79087</v>
@@ -19844,16 +19840,19 @@
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>434836</v>
+        <v>435236</v>
       </c>
       <c r="R196" t="n">
-        <v>6782524</v>
+        <v>6782220</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -19880,12 +19879,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -19894,6 +19893,7 @@
       <c r="AE196" t="b">
         <v>0</v>
       </c>
+      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -19912,10 +19912,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129996263</v>
+        <v>129996425</v>
       </c>
       <c r="B197" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19923,21 +19923,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -19947,10 +19947,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>435076</v>
+        <v>434836</v>
       </c>
       <c r="R197" t="n">
-        <v>6782532</v>
+        <v>6782524</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -19977,12 +19977,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20009,7 +20009,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129996268</v>
+        <v>129996244</v>
       </c>
       <c r="B198" t="n">
         <v>79706</v>
@@ -20044,10 +20044,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>435103</v>
+        <v>434789</v>
       </c>
       <c r="R198" t="n">
-        <v>6782305</v>
+        <v>6782590</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20074,12 +20074,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -20106,10 +20106,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129996376</v>
+        <v>129996216</v>
       </c>
       <c r="B199" t="n">
-        <v>78844</v>
+        <v>79706</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20117,21 +20117,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20141,10 +20141,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>435039</v>
+        <v>434928</v>
       </c>
       <c r="R199" t="n">
-        <v>6782675</v>
+        <v>6782707</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20171,12 +20171,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD199" t="b">

--- a/artfynd/A 59104-2025 artfynd.xlsx
+++ b/artfynd/A 59104-2025 artfynd.xlsx
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129996281</v>
+        <v>129996213</v>
       </c>
       <c r="B3" t="n">
-        <v>79707</v>
+        <v>91570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435132</v>
+        <v>434850</v>
       </c>
       <c r="R3" t="n">
-        <v>6782205</v>
+        <v>6782509</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -841,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -855,8 +855,24 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -873,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129996231</v>
+        <v>129996281</v>
       </c>
       <c r="B4" t="n">
         <v>79707</v>
@@ -908,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434855</v>
+        <v>435132</v>
       </c>
       <c r="R4" t="n">
-        <v>6782501</v>
+        <v>6782205</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -938,12 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -970,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129996426</v>
+        <v>129996231</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434834</v>
+        <v>434855</v>
       </c>
       <c r="R5" t="n">
-        <v>6782525</v>
+        <v>6782501</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129996423</v>
+        <v>129996426</v>
       </c>
       <c r="B6" t="n">
         <v>79088</v>
@@ -1102,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434722</v>
+        <v>434834</v>
       </c>
       <c r="R6" t="n">
-        <v>6782572</v>
+        <v>6782525</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,7 +1180,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129996420</v>
+        <v>129996423</v>
       </c>
       <c r="B7" t="n">
         <v>79088</v>
@@ -1199,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434663</v>
+        <v>434722</v>
       </c>
       <c r="R7" t="n">
-        <v>6782668</v>
+        <v>6782572</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129996435</v>
+        <v>129996420</v>
       </c>
       <c r="B8" t="n">
         <v>79088</v>
@@ -1296,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434970</v>
+        <v>434663</v>
       </c>
       <c r="R8" t="n">
-        <v>6782543</v>
+        <v>6782668</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,7 +1374,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129996421</v>
+        <v>129996435</v>
       </c>
       <c r="B9" t="n">
         <v>79088</v>
@@ -1393,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434631</v>
+        <v>434970</v>
       </c>
       <c r="R9" t="n">
-        <v>6782620</v>
+        <v>6782543</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,7 +1471,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129996445</v>
+        <v>129996421</v>
       </c>
       <c r="B10" t="n">
         <v>79088</v>
@@ -1490,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435022</v>
+        <v>434631</v>
       </c>
       <c r="R10" t="n">
-        <v>6782661</v>
+        <v>6782620</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1520,12 +1536,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1552,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129996483</v>
+        <v>129996445</v>
       </c>
       <c r="B11" t="n">
-        <v>78095</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1563,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1587,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434752</v>
+        <v>435022</v>
       </c>
       <c r="R11" t="n">
-        <v>6782544</v>
+        <v>6782661</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1617,12 +1633,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1649,32 +1665,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129996213</v>
+        <v>129996483</v>
       </c>
       <c r="B12" t="n">
-        <v>91570</v>
+        <v>78095</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6487</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1684,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434850</v>
+        <v>434752</v>
       </c>
       <c r="R12" t="n">
-        <v>6782509</v>
+        <v>6782544</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1728,24 +1744,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1762,41 +1762,40 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129996362</v>
+        <v>129996323</v>
       </c>
       <c r="B13" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1806,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434988</v>
+        <v>435142</v>
       </c>
       <c r="R13" t="n">
-        <v>6782383</v>
+        <v>6782181</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,7 +1849,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1869,40 +1867,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129996323</v>
+        <v>129996362</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1912,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435142</v>
+        <v>434988</v>
       </c>
       <c r="R14" t="n">
-        <v>6782181</v>
+        <v>6782383</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,6 +1955,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2459,10 +2459,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129996294</v>
+        <v>129996385</v>
       </c>
       <c r="B20" t="n">
-        <v>79678</v>
+        <v>78845</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2470,21 +2470,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434962</v>
+        <v>435158</v>
       </c>
       <c r="R20" t="n">
-        <v>6782387</v>
+        <v>6782371</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2556,10 +2556,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129996349</v>
+        <v>129996224</v>
       </c>
       <c r="B21" t="n">
-        <v>78846</v>
+        <v>79707</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2567,21 +2567,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435210</v>
+        <v>434648</v>
       </c>
       <c r="R21" t="n">
-        <v>6782209</v>
+        <v>6782668</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2621,12 +2621,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2653,10 +2653,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129996339</v>
+        <v>129996374</v>
       </c>
       <c r="B22" t="n">
-        <v>78846</v>
+        <v>78845</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2664,21 +2664,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435050</v>
+        <v>434788</v>
       </c>
       <c r="R22" t="n">
-        <v>6782437</v>
+        <v>6782592</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2750,10 +2750,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129996385</v>
+        <v>129996265</v>
       </c>
       <c r="B23" t="n">
-        <v>78845</v>
+        <v>79707</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435158</v>
+        <v>435021</v>
       </c>
       <c r="R23" t="n">
-        <v>6782371</v>
+        <v>6782417</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2847,10 +2847,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129996224</v>
+        <v>129996294</v>
       </c>
       <c r="B24" t="n">
-        <v>79707</v>
+        <v>79678</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2858,21 +2858,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434648</v>
+        <v>434962</v>
       </c>
       <c r="R24" t="n">
-        <v>6782668</v>
+        <v>6782387</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2912,12 +2912,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2944,10 +2944,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129996374</v>
+        <v>129996349</v>
       </c>
       <c r="B25" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2955,21 +2955,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434788</v>
+        <v>435210</v>
       </c>
       <c r="R25" t="n">
-        <v>6782592</v>
+        <v>6782209</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3041,10 +3041,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129996265</v>
+        <v>129996339</v>
       </c>
       <c r="B26" t="n">
-        <v>79707</v>
+        <v>78846</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3052,21 +3052,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435021</v>
+        <v>435050</v>
       </c>
       <c r="R26" t="n">
-        <v>6782417</v>
+        <v>6782437</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129996226</v>
+        <v>129996324</v>
       </c>
       <c r="B27" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3149,34 +3149,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434636</v>
+        <v>435143</v>
       </c>
       <c r="R27" t="n">
-        <v>6782611</v>
+        <v>6782303</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3203,12 +3211,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3235,45 +3243,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129996227</v>
+        <v>129996359</v>
       </c>
       <c r="B28" t="n">
-        <v>79707</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434657</v>
+        <v>434911</v>
       </c>
       <c r="R28" t="n">
-        <v>6782585</v>
+        <v>6782571</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3314,6 +3331,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3332,45 +3350,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129996214</v>
+        <v>129996353</v>
       </c>
       <c r="B29" t="n">
-        <v>79707</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435028</v>
+        <v>434838</v>
       </c>
       <c r="R29" t="n">
-        <v>6782399</v>
+        <v>6782905</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3411,6 +3438,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3429,10 +3457,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129996371</v>
+        <v>129996311</v>
       </c>
       <c r="B30" t="n">
-        <v>78845</v>
+        <v>57898</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3440,34 +3468,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434852</v>
+        <v>435065</v>
       </c>
       <c r="R30" t="n">
-        <v>6782499</v>
+        <v>6782516</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3494,12 +3530,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3526,10 +3562,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129996463</v>
+        <v>129996295</v>
       </c>
       <c r="B31" t="n">
-        <v>79088</v>
+        <v>79678</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3537,21 +3573,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3561,10 +3597,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435172</v>
+        <v>434994</v>
       </c>
       <c r="R31" t="n">
-        <v>6782321</v>
+        <v>6782360</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3623,10 +3659,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129996444</v>
+        <v>129996226</v>
       </c>
       <c r="B32" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3634,21 +3670,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3658,10 +3694,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435010</v>
+        <v>434636</v>
       </c>
       <c r="R32" t="n">
-        <v>6782685</v>
+        <v>6782611</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3688,12 +3724,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3720,10 +3756,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129996324</v>
+        <v>129996227</v>
       </c>
       <c r="B33" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3731,42 +3767,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435143</v>
+        <v>434657</v>
       </c>
       <c r="R33" t="n">
-        <v>6782303</v>
+        <v>6782585</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,12 +3821,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3825,10 +3853,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129996311</v>
+        <v>129996214</v>
       </c>
       <c r="B34" t="n">
-        <v>57898</v>
+        <v>79707</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3836,42 +3864,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435065</v>
+        <v>435028</v>
       </c>
       <c r="R34" t="n">
-        <v>6782516</v>
+        <v>6782399</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3898,12 +3918,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3930,10 +3950,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129996295</v>
+        <v>129996371</v>
       </c>
       <c r="B35" t="n">
-        <v>79678</v>
+        <v>78845</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3941,21 +3961,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3965,10 +3985,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434994</v>
+        <v>434852</v>
       </c>
       <c r="R35" t="n">
-        <v>6782360</v>
+        <v>6782499</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3995,12 +4015,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4027,54 +4047,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129996359</v>
+        <v>129996463</v>
       </c>
       <c r="B36" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>434911</v>
+        <v>435172</v>
       </c>
       <c r="R36" t="n">
-        <v>6782571</v>
+        <v>6782321</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4101,12 +4112,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4115,7 +4126,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4134,54 +4144,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129996353</v>
+        <v>129996444</v>
       </c>
       <c r="B37" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434838</v>
+        <v>435010</v>
       </c>
       <c r="R37" t="n">
-        <v>6782905</v>
+        <v>6782685</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4208,12 +4209,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4222,7 +4223,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5147,54 +5147,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129996360</v>
+        <v>129996347</v>
       </c>
       <c r="B47" t="n">
-        <v>8451</v>
+        <v>78846</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435016</v>
+        <v>435217</v>
       </c>
       <c r="R47" t="n">
-        <v>6782447</v>
+        <v>6782258</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5235,7 +5226,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5254,10 +5244,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129996320</v>
+        <v>129996297</v>
       </c>
       <c r="B48" t="n">
-        <v>57737</v>
+        <v>79678</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5265,42 +5255,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435015</v>
+        <v>435187</v>
       </c>
       <c r="R48" t="n">
-        <v>6782457</v>
+        <v>6782242</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5359,10 +5341,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129996347</v>
+        <v>129996284</v>
       </c>
       <c r="B49" t="n">
-        <v>78846</v>
+        <v>79678</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5370,21 +5352,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5394,10 +5376,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435217</v>
+        <v>434655</v>
       </c>
       <c r="R49" t="n">
-        <v>6782258</v>
+        <v>6782666</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5424,12 +5406,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5456,7 +5438,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129996297</v>
+        <v>129996288</v>
       </c>
       <c r="B50" t="n">
         <v>79678</v>
@@ -5491,10 +5473,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435187</v>
+        <v>434753</v>
       </c>
       <c r="R50" t="n">
-        <v>6782242</v>
+        <v>6782550</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5521,12 +5503,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5553,10 +5535,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129996284</v>
+        <v>129996340</v>
       </c>
       <c r="B51" t="n">
-        <v>79678</v>
+        <v>78846</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5564,21 +5546,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5588,10 +5570,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434655</v>
+        <v>434965</v>
       </c>
       <c r="R51" t="n">
-        <v>6782666</v>
+        <v>6782389</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5618,12 +5600,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5650,10 +5632,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129996288</v>
+        <v>129996320</v>
       </c>
       <c r="B52" t="n">
-        <v>79678</v>
+        <v>57737</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5661,34 +5643,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434753</v>
+        <v>435015</v>
       </c>
       <c r="R52" t="n">
-        <v>6782550</v>
+        <v>6782457</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5715,12 +5705,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5747,45 +5737,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129996340</v>
+        <v>129996360</v>
       </c>
       <c r="B53" t="n">
-        <v>78846</v>
+        <v>8451</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434965</v>
+        <v>435016</v>
       </c>
       <c r="R53" t="n">
-        <v>6782389</v>
+        <v>6782447</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5826,6 +5825,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -12244,48 +12244,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129996481</v>
+        <v>129996271</v>
       </c>
       <c r="B119" t="n">
-        <v>92888</v>
+        <v>79707</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>434976</v>
+        <v>435189</v>
       </c>
       <c r="R119" t="n">
-        <v>6782376</v>
+        <v>6782244</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12326,7 +12323,6 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12345,7 +12341,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129996271</v>
+        <v>129996259</v>
       </c>
       <c r="B120" t="n">
         <v>79707</v>
@@ -12380,10 +12376,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>435189</v>
+        <v>435020</v>
       </c>
       <c r="R120" t="n">
-        <v>6782244</v>
+        <v>6782612</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12442,10 +12438,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129996259</v>
+        <v>129996447</v>
       </c>
       <c r="B121" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12453,21 +12449,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12477,10 +12473,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>435020</v>
+        <v>435039</v>
       </c>
       <c r="R121" t="n">
-        <v>6782612</v>
+        <v>6782658</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12539,7 +12535,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129996447</v>
+        <v>129996403</v>
       </c>
       <c r="B122" t="n">
         <v>79088</v>
@@ -12574,10 +12570,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>435039</v>
+        <v>435025</v>
       </c>
       <c r="R122" t="n">
-        <v>6782658</v>
+        <v>6782389</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12604,12 +12600,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12636,10 +12632,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129996403</v>
+        <v>129996348</v>
       </c>
       <c r="B123" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12647,21 +12643,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12671,10 +12667,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>435025</v>
+        <v>435230</v>
       </c>
       <c r="R123" t="n">
-        <v>6782389</v>
+        <v>6782260</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12701,12 +12697,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12733,7 +12729,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129996348</v>
+        <v>129996342</v>
       </c>
       <c r="B124" t="n">
         <v>78846</v>
@@ -12768,10 +12764,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>435230</v>
+        <v>435104</v>
       </c>
       <c r="R124" t="n">
-        <v>6782260</v>
+        <v>6782300</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12830,7 +12826,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129996342</v>
+        <v>129996332</v>
       </c>
       <c r="B125" t="n">
         <v>78846</v>
@@ -12865,10 +12861,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>435104</v>
+        <v>434796</v>
       </c>
       <c r="R125" t="n">
-        <v>6782300</v>
+        <v>6782579</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12895,12 +12891,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -12927,7 +12923,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129996332</v>
+        <v>129996334</v>
       </c>
       <c r="B126" t="n">
         <v>78846</v>
@@ -12956,16 +12952,19 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>434796</v>
+        <v>434994</v>
       </c>
       <c r="R126" t="n">
-        <v>6782579</v>
+        <v>6782543</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13006,6 +13005,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13024,10 +13024,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129996334</v>
+        <v>129996298</v>
       </c>
       <c r="B127" t="n">
-        <v>78846</v>
+        <v>79678</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13035,37 +13035,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>434994</v>
+        <v>435213</v>
       </c>
       <c r="R127" t="n">
-        <v>6782543</v>
+        <v>6782254</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13092,12 +13089,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13106,7 +13103,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13125,45 +13121,48 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129996298</v>
+        <v>129996481</v>
       </c>
       <c r="B128" t="n">
-        <v>79678</v>
+        <v>92888</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>435213</v>
+        <v>434976</v>
       </c>
       <c r="R128" t="n">
-        <v>6782254</v>
+        <v>6782376</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13204,6 +13203,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13222,10 +13222,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129996279</v>
+        <v>129996331</v>
       </c>
       <c r="B129" t="n">
-        <v>79707</v>
+        <v>78846</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13233,21 +13233,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13257,10 +13257,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>435130</v>
+        <v>434773</v>
       </c>
       <c r="R129" t="n">
-        <v>6782186</v>
+        <v>6782567</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13319,10 +13319,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129996476</v>
+        <v>129996279</v>
       </c>
       <c r="B130" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13330,21 +13330,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13354,10 +13354,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>435079</v>
+        <v>435130</v>
       </c>
       <c r="R130" t="n">
-        <v>6782284</v>
+        <v>6782186</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13390,11 +13390,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13809,10 +13804,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129996331</v>
+        <v>129996476</v>
       </c>
       <c r="B135" t="n">
-        <v>78846</v>
+        <v>79088</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13820,21 +13815,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13844,10 +13839,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>434773</v>
+        <v>435079</v>
       </c>
       <c r="R135" t="n">
-        <v>6782567</v>
+        <v>6782284</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13874,12 +13869,17 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14687,10 +14687,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129996458</v>
+        <v>129996243</v>
       </c>
       <c r="B144" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14698,21 +14698,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14722,10 +14722,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>434987</v>
+        <v>434780</v>
       </c>
       <c r="R144" t="n">
-        <v>6782372</v>
+        <v>6782593</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14752,12 +14752,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -14784,10 +14784,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129996412</v>
+        <v>129996381</v>
       </c>
       <c r="B145" t="n">
-        <v>79088</v>
+        <v>78845</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14795,37 +14795,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>434847</v>
+        <v>434974</v>
       </c>
       <c r="R145" t="n">
-        <v>6782878</v>
+        <v>6782389</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14852,17 +14849,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -14871,7 +14863,6 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -14890,7 +14881,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129996460</v>
+        <v>129996411</v>
       </c>
       <c r="B146" t="n">
         <v>79088</v>
@@ -14925,10 +14916,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>435106</v>
+        <v>434854</v>
       </c>
       <c r="R146" t="n">
-        <v>6782315</v>
+        <v>6782808</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14955,12 +14946,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -14987,7 +14978,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129996411</v>
+        <v>129996458</v>
       </c>
       <c r="B147" t="n">
         <v>79088</v>
@@ -15022,10 +15013,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>434854</v>
+        <v>434987</v>
       </c>
       <c r="R147" t="n">
-        <v>6782808</v>
+        <v>6782372</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15052,12 +15043,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15084,10 +15075,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129996317</v>
+        <v>129996412</v>
       </c>
       <c r="B148" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15095,31 +15086,26 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
@@ -15127,10 +15113,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>434837</v>
+        <v>434847</v>
       </c>
       <c r="R148" t="n">
-        <v>6782880</v>
+        <v>6782878</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15165,12 +15151,18 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -15189,10 +15181,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129996243</v>
+        <v>129996460</v>
       </c>
       <c r="B149" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15200,21 +15192,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15224,10 +15216,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>434780</v>
+        <v>435106</v>
       </c>
       <c r="R149" t="n">
-        <v>6782593</v>
+        <v>6782315</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15254,12 +15246,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15286,10 +15278,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129996381</v>
+        <v>129996317</v>
       </c>
       <c r="B150" t="n">
-        <v>78845</v>
+        <v>57737</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15297,34 +15289,42 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>434974</v>
+        <v>434837</v>
       </c>
       <c r="R150" t="n">
-        <v>6782389</v>
+        <v>6782880</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15351,12 +15351,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15383,45 +15383,54 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129996289</v>
+        <v>129996361</v>
       </c>
       <c r="B151" t="n">
-        <v>79678</v>
+        <v>8451</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>434909</v>
+        <v>435003</v>
       </c>
       <c r="R151" t="n">
-        <v>6782588</v>
+        <v>6782399</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15448,12 +15457,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15462,6 +15471,7 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -15480,54 +15490,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129996361</v>
+        <v>129996289</v>
       </c>
       <c r="B152" t="n">
-        <v>8451</v>
+        <v>79678</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>435003</v>
+        <v>434909</v>
       </c>
       <c r="R152" t="n">
-        <v>6782399</v>
+        <v>6782588</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15554,12 +15555,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15568,7 +15569,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -18634,10 +18634,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129996252</v>
+        <v>129996290</v>
       </c>
       <c r="B184" t="n">
-        <v>79707</v>
+        <v>79678</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18645,21 +18645,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18669,10 +18669,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>435114</v>
+        <v>434998</v>
       </c>
       <c r="R184" t="n">
-        <v>6782479</v>
+        <v>6782675</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18731,10 +18731,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129996277</v>
+        <v>129996429</v>
       </c>
       <c r="B185" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18742,21 +18742,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -18766,10 +18766,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>435153</v>
+        <v>434796</v>
       </c>
       <c r="R185" t="n">
-        <v>6782169</v>
+        <v>6782586</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -18796,12 +18796,17 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -18828,10 +18833,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129996273</v>
+        <v>129996467</v>
       </c>
       <c r="B186" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18839,21 +18844,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -18863,10 +18868,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>435238</v>
+        <v>435205</v>
       </c>
       <c r="R186" t="n">
-        <v>6782244</v>
+        <v>6782175</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18925,7 +18930,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129996235</v>
+        <v>129996252</v>
       </c>
       <c r="B187" t="n">
         <v>79707</v>
@@ -18960,10 +18965,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>434763</v>
+        <v>435114</v>
       </c>
       <c r="R187" t="n">
-        <v>6782543</v>
+        <v>6782479</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -18990,12 +18995,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19022,10 +19027,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129996322</v>
+        <v>129996277</v>
       </c>
       <c r="B188" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19033,42 +19038,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>434994</v>
+        <v>435153</v>
       </c>
       <c r="R188" t="n">
-        <v>6782340</v>
+        <v>6782169</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19127,10 +19124,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129996429</v>
+        <v>129996273</v>
       </c>
       <c r="B189" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19138,21 +19135,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19162,10 +19159,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>434796</v>
+        <v>435238</v>
       </c>
       <c r="R189" t="n">
-        <v>6782586</v>
+        <v>6782244</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19192,17 +19189,12 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -19229,10 +19221,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129996467</v>
+        <v>129996235</v>
       </c>
       <c r="B190" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19240,21 +19232,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19264,10 +19256,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>435205</v>
+        <v>434763</v>
       </c>
       <c r="R190" t="n">
-        <v>6782175</v>
+        <v>6782543</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19294,12 +19286,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -19326,10 +19318,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129996290</v>
+        <v>129996322</v>
       </c>
       <c r="B191" t="n">
-        <v>79678</v>
+        <v>57737</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19337,34 +19329,42 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>434998</v>
+        <v>434994</v>
       </c>
       <c r="R191" t="n">
-        <v>6782675</v>
+        <v>6782340</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20203,10 +20203,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129996219</v>
+        <v>129996471</v>
       </c>
       <c r="B200" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20214,21 +20214,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20238,10 +20238,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>434922</v>
+        <v>435126</v>
       </c>
       <c r="R200" t="n">
-        <v>6782675</v>
+        <v>6782203</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20268,12 +20268,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -20300,10 +20300,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129996272</v>
+        <v>129996325</v>
       </c>
       <c r="B201" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20311,34 +20311,42 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>435213</v>
+        <v>434755</v>
       </c>
       <c r="R201" t="n">
-        <v>6782257</v>
+        <v>6782589</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20365,12 +20373,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -20397,10 +20405,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129996471</v>
+        <v>129996219</v>
       </c>
       <c r="B202" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20408,21 +20416,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20432,10 +20440,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>435126</v>
+        <v>434922</v>
       </c>
       <c r="R202" t="n">
-        <v>6782203</v>
+        <v>6782675</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20462,12 +20470,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -20494,10 +20502,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129996325</v>
+        <v>129996272</v>
       </c>
       <c r="B203" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20505,42 +20513,34 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>434755</v>
+        <v>435213</v>
       </c>
       <c r="R203" t="n">
-        <v>6782589</v>
+        <v>6782257</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20567,12 +20567,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD203" t="b">

--- a/artfynd/A 59104-2025 artfynd.xlsx
+++ b/artfynd/A 59104-2025 artfynd.xlsx
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129996213</v>
+        <v>129996281</v>
       </c>
       <c r="B3" t="n">
-        <v>91570</v>
+        <v>79707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434850</v>
+        <v>435132</v>
       </c>
       <c r="R3" t="n">
-        <v>6782509</v>
+        <v>6782205</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -841,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -855,24 +855,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -889,7 +873,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129996281</v>
+        <v>129996231</v>
       </c>
       <c r="B4" t="n">
         <v>79707</v>
@@ -924,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435132</v>
+        <v>434855</v>
       </c>
       <c r="R4" t="n">
-        <v>6782205</v>
+        <v>6782501</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,12 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129996231</v>
+        <v>129996426</v>
       </c>
       <c r="B5" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434855</v>
+        <v>434834</v>
       </c>
       <c r="R5" t="n">
-        <v>6782501</v>
+        <v>6782525</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1067,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129996426</v>
+        <v>129996423</v>
       </c>
       <c r="B6" t="n">
         <v>79088</v>
@@ -1118,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434834</v>
+        <v>434722</v>
       </c>
       <c r="R6" t="n">
-        <v>6782525</v>
+        <v>6782572</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,7 +1164,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129996423</v>
+        <v>129996420</v>
       </c>
       <c r="B7" t="n">
         <v>79088</v>
@@ -1215,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434722</v>
+        <v>434663</v>
       </c>
       <c r="R7" t="n">
-        <v>6782572</v>
+        <v>6782668</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,7 +1261,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129996420</v>
+        <v>129996435</v>
       </c>
       <c r="B8" t="n">
         <v>79088</v>
@@ -1312,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434663</v>
+        <v>434970</v>
       </c>
       <c r="R8" t="n">
-        <v>6782668</v>
+        <v>6782543</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,7 +1358,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129996435</v>
+        <v>129996421</v>
       </c>
       <c r="B9" t="n">
         <v>79088</v>
@@ -1409,10 +1393,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434970</v>
+        <v>434631</v>
       </c>
       <c r="R9" t="n">
-        <v>6782543</v>
+        <v>6782620</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,7 +1455,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129996421</v>
+        <v>129996445</v>
       </c>
       <c r="B10" t="n">
         <v>79088</v>
@@ -1506,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434631</v>
+        <v>435022</v>
       </c>
       <c r="R10" t="n">
-        <v>6782620</v>
+        <v>6782661</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,12 +1520,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,10 +1552,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129996445</v>
+        <v>129996483</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>78095</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,21 +1563,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435022</v>
+        <v>434752</v>
       </c>
       <c r="R11" t="n">
-        <v>6782661</v>
+        <v>6782544</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,12 +1617,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,32 +1649,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129996483</v>
+        <v>129996213</v>
       </c>
       <c r="B12" t="n">
-        <v>78095</v>
+        <v>91570</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6487</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1684,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434752</v>
+        <v>434850</v>
       </c>
       <c r="R12" t="n">
-        <v>6782544</v>
+        <v>6782509</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1744,8 +1728,24 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1762,40 +1762,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129996323</v>
+        <v>129996362</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1805,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435142</v>
+        <v>434988</v>
       </c>
       <c r="R13" t="n">
-        <v>6782181</v>
+        <v>6782383</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,6 +1850,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1867,41 +1869,40 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129996362</v>
+        <v>129996323</v>
       </c>
       <c r="B14" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1911,10 +1912,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434988</v>
+        <v>435142</v>
       </c>
       <c r="R14" t="n">
-        <v>6782383</v>
+        <v>6782181</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1956,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2459,10 +2459,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129996385</v>
+        <v>129996294</v>
       </c>
       <c r="B20" t="n">
-        <v>78845</v>
+        <v>79678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2470,21 +2470,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435158</v>
+        <v>434962</v>
       </c>
       <c r="R20" t="n">
-        <v>6782371</v>
+        <v>6782387</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2556,10 +2556,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129996224</v>
+        <v>129996349</v>
       </c>
       <c r="B21" t="n">
-        <v>79707</v>
+        <v>78846</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2567,21 +2567,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434648</v>
+        <v>435210</v>
       </c>
       <c r="R21" t="n">
-        <v>6782668</v>
+        <v>6782209</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2621,12 +2621,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2653,10 +2653,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129996374</v>
+        <v>129996339</v>
       </c>
       <c r="B22" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2664,21 +2664,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434788</v>
+        <v>435050</v>
       </c>
       <c r="R22" t="n">
-        <v>6782592</v>
+        <v>6782437</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2750,10 +2750,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129996265</v>
+        <v>129996385</v>
       </c>
       <c r="B23" t="n">
-        <v>79707</v>
+        <v>78845</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435021</v>
+        <v>435158</v>
       </c>
       <c r="R23" t="n">
-        <v>6782417</v>
+        <v>6782371</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2847,10 +2847,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129996294</v>
+        <v>129996224</v>
       </c>
       <c r="B24" t="n">
-        <v>79678</v>
+        <v>79707</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2858,21 +2858,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434962</v>
+        <v>434648</v>
       </c>
       <c r="R24" t="n">
-        <v>6782387</v>
+        <v>6782668</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2912,12 +2912,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2944,10 +2944,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129996349</v>
+        <v>129996374</v>
       </c>
       <c r="B25" t="n">
-        <v>78846</v>
+        <v>78845</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2955,21 +2955,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435210</v>
+        <v>434788</v>
       </c>
       <c r="R25" t="n">
-        <v>6782209</v>
+        <v>6782592</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3041,10 +3041,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129996339</v>
+        <v>129996265</v>
       </c>
       <c r="B26" t="n">
-        <v>78846</v>
+        <v>79707</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3052,21 +3052,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435050</v>
+        <v>435021</v>
       </c>
       <c r="R26" t="n">
-        <v>6782437</v>
+        <v>6782417</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -5147,10 +5147,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129996347</v>
+        <v>129996320</v>
       </c>
       <c r="B47" t="n">
-        <v>78846</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5158,34 +5158,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435217</v>
+        <v>435015</v>
       </c>
       <c r="R47" t="n">
-        <v>6782258</v>
+        <v>6782457</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5244,10 +5252,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129996297</v>
+        <v>129996347</v>
       </c>
       <c r="B48" t="n">
-        <v>79678</v>
+        <v>78846</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5255,21 +5263,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5279,10 +5287,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435187</v>
+        <v>435217</v>
       </c>
       <c r="R48" t="n">
-        <v>6782242</v>
+        <v>6782258</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5341,7 +5349,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129996284</v>
+        <v>129996297</v>
       </c>
       <c r="B49" t="n">
         <v>79678</v>
@@ -5376,10 +5384,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434655</v>
+        <v>435187</v>
       </c>
       <c r="R49" t="n">
-        <v>6782666</v>
+        <v>6782242</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5406,12 +5414,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5438,7 +5446,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129996288</v>
+        <v>129996284</v>
       </c>
       <c r="B50" t="n">
         <v>79678</v>
@@ -5473,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434753</v>
+        <v>434655</v>
       </c>
       <c r="R50" t="n">
-        <v>6782550</v>
+        <v>6782666</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5535,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129996340</v>
+        <v>129996288</v>
       </c>
       <c r="B51" t="n">
-        <v>78846</v>
+        <v>79678</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5546,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5570,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434965</v>
+        <v>434753</v>
       </c>
       <c r="R51" t="n">
-        <v>6782389</v>
+        <v>6782550</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5600,12 +5608,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5632,10 +5640,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129996320</v>
+        <v>129996340</v>
       </c>
       <c r="B52" t="n">
-        <v>57737</v>
+        <v>78846</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5643,42 +5651,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435015</v>
+        <v>434965</v>
       </c>
       <c r="R52" t="n">
-        <v>6782457</v>
+        <v>6782389</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -12244,45 +12244,48 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129996271</v>
+        <v>129996481</v>
       </c>
       <c r="B119" t="n">
-        <v>79707</v>
+        <v>92888</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>435189</v>
+        <v>434976</v>
       </c>
       <c r="R119" t="n">
-        <v>6782244</v>
+        <v>6782376</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12323,6 +12326,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12341,7 +12345,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129996259</v>
+        <v>129996271</v>
       </c>
       <c r="B120" t="n">
         <v>79707</v>
@@ -12376,10 +12380,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>435020</v>
+        <v>435189</v>
       </c>
       <c r="R120" t="n">
-        <v>6782612</v>
+        <v>6782244</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12438,10 +12442,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129996447</v>
+        <v>129996259</v>
       </c>
       <c r="B121" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12449,21 +12453,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12473,10 +12477,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>435039</v>
+        <v>435020</v>
       </c>
       <c r="R121" t="n">
-        <v>6782658</v>
+        <v>6782612</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12535,7 +12539,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129996403</v>
+        <v>129996447</v>
       </c>
       <c r="B122" t="n">
         <v>79088</v>
@@ -12570,10 +12574,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>435025</v>
+        <v>435039</v>
       </c>
       <c r="R122" t="n">
-        <v>6782389</v>
+        <v>6782658</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12600,12 +12604,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12632,10 +12636,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129996348</v>
+        <v>129996403</v>
       </c>
       <c r="B123" t="n">
-        <v>78846</v>
+        <v>79088</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12643,21 +12647,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12667,10 +12671,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>435230</v>
+        <v>435025</v>
       </c>
       <c r="R123" t="n">
-        <v>6782260</v>
+        <v>6782389</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12697,12 +12701,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12729,7 +12733,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129996342</v>
+        <v>129996348</v>
       </c>
       <c r="B124" t="n">
         <v>78846</v>
@@ -12764,10 +12768,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>435104</v>
+        <v>435230</v>
       </c>
       <c r="R124" t="n">
-        <v>6782300</v>
+        <v>6782260</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12826,7 +12830,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129996332</v>
+        <v>129996342</v>
       </c>
       <c r="B125" t="n">
         <v>78846</v>
@@ -12861,10 +12865,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>434796</v>
+        <v>435104</v>
       </c>
       <c r="R125" t="n">
-        <v>6782579</v>
+        <v>6782300</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12891,12 +12895,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -12923,7 +12927,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129996334</v>
+        <v>129996332</v>
       </c>
       <c r="B126" t="n">
         <v>78846</v>
@@ -12952,19 +12956,16 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>434994</v>
+        <v>434796</v>
       </c>
       <c r="R126" t="n">
-        <v>6782543</v>
+        <v>6782579</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13005,7 +13006,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13024,10 +13024,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129996298</v>
+        <v>129996334</v>
       </c>
       <c r="B127" t="n">
-        <v>79678</v>
+        <v>78846</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13035,34 +13035,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>435213</v>
+        <v>434994</v>
       </c>
       <c r="R127" t="n">
-        <v>6782254</v>
+        <v>6782543</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13089,12 +13092,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13103,6 +13106,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13121,48 +13125,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129996481</v>
+        <v>129996298</v>
       </c>
       <c r="B128" t="n">
-        <v>92888</v>
+        <v>79678</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>434976</v>
+        <v>435213</v>
       </c>
       <c r="R128" t="n">
-        <v>6782376</v>
+        <v>6782254</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13203,7 +13204,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13222,10 +13222,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129996331</v>
+        <v>129996279</v>
       </c>
       <c r="B129" t="n">
-        <v>78846</v>
+        <v>79707</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13233,21 +13233,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13257,10 +13257,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>434773</v>
+        <v>435130</v>
       </c>
       <c r="R129" t="n">
-        <v>6782567</v>
+        <v>6782186</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13319,10 +13319,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129996279</v>
+        <v>129996476</v>
       </c>
       <c r="B130" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13330,21 +13330,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13354,10 +13354,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>435130</v>
+        <v>435079</v>
       </c>
       <c r="R130" t="n">
-        <v>6782186</v>
+        <v>6782284</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13390,6 +13390,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13804,10 +13809,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129996476</v>
+        <v>129996331</v>
       </c>
       <c r="B135" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13815,21 +13820,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13839,10 +13844,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>435079</v>
+        <v>434773</v>
       </c>
       <c r="R135" t="n">
-        <v>6782284</v>
+        <v>6782567</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13869,17 +13874,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14687,10 +14687,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129996243</v>
+        <v>129996289</v>
       </c>
       <c r="B144" t="n">
-        <v>79707</v>
+        <v>79678</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14698,21 +14698,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14722,10 +14722,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>434780</v>
+        <v>434909</v>
       </c>
       <c r="R144" t="n">
-        <v>6782593</v>
+        <v>6782588</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14784,10 +14784,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129996381</v>
+        <v>129996243</v>
       </c>
       <c r="B145" t="n">
-        <v>78845</v>
+        <v>79707</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14795,21 +14795,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14819,10 +14819,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>434974</v>
+        <v>434780</v>
       </c>
       <c r="R145" t="n">
-        <v>6782389</v>
+        <v>6782593</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14849,12 +14849,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -14881,10 +14881,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129996411</v>
+        <v>129996381</v>
       </c>
       <c r="B146" t="n">
-        <v>79088</v>
+        <v>78845</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14892,21 +14892,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14916,10 +14916,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>434854</v>
+        <v>434974</v>
       </c>
       <c r="R146" t="n">
-        <v>6782808</v>
+        <v>6782389</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14946,12 +14946,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15278,10 +15278,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129996317</v>
+        <v>129996411</v>
       </c>
       <c r="B150" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15289,42 +15289,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>434837</v>
+        <v>434854</v>
       </c>
       <c r="R150" t="n">
-        <v>6782880</v>
+        <v>6782808</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15383,41 +15375,40 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129996361</v>
+        <v>129996317</v>
       </c>
       <c r="B151" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -15427,10 +15418,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>435003</v>
+        <v>434837</v>
       </c>
       <c r="R151" t="n">
-        <v>6782399</v>
+        <v>6782880</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15457,12 +15448,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15471,7 +15462,6 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -15490,45 +15480,54 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129996289</v>
+        <v>129996361</v>
       </c>
       <c r="B152" t="n">
-        <v>79678</v>
+        <v>8451</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>434909</v>
+        <v>435003</v>
       </c>
       <c r="R152" t="n">
-        <v>6782588</v>
+        <v>6782399</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15555,12 +15554,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15569,6 +15568,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -18634,10 +18634,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129996290</v>
+        <v>129996252</v>
       </c>
       <c r="B184" t="n">
-        <v>79678</v>
+        <v>79707</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18645,21 +18645,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18669,10 +18669,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>434998</v>
+        <v>435114</v>
       </c>
       <c r="R184" t="n">
-        <v>6782675</v>
+        <v>6782479</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18731,10 +18731,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129996429</v>
+        <v>129996277</v>
       </c>
       <c r="B185" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18742,21 +18742,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -18766,10 +18766,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>434796</v>
+        <v>435153</v>
       </c>
       <c r="R185" t="n">
-        <v>6782586</v>
+        <v>6782169</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -18796,17 +18796,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -18833,10 +18828,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129996467</v>
+        <v>129996273</v>
       </c>
       <c r="B186" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18844,21 +18839,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -18868,10 +18863,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>435205</v>
+        <v>435238</v>
       </c>
       <c r="R186" t="n">
-        <v>6782175</v>
+        <v>6782244</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18930,7 +18925,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129996252</v>
+        <v>129996235</v>
       </c>
       <c r="B187" t="n">
         <v>79707</v>
@@ -18965,10 +18960,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>435114</v>
+        <v>434763</v>
       </c>
       <c r="R187" t="n">
-        <v>6782479</v>
+        <v>6782543</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -18995,12 +18990,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19027,10 +19022,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129996277</v>
+        <v>129996322</v>
       </c>
       <c r="B188" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19038,34 +19033,42 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>435153</v>
+        <v>434994</v>
       </c>
       <c r="R188" t="n">
-        <v>6782169</v>
+        <v>6782340</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19124,10 +19127,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129996273</v>
+        <v>129996429</v>
       </c>
       <c r="B189" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19135,21 +19138,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19159,10 +19162,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>435238</v>
+        <v>434796</v>
       </c>
       <c r="R189" t="n">
-        <v>6782244</v>
+        <v>6782586</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19189,12 +19192,17 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -19221,10 +19229,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129996235</v>
+        <v>129996467</v>
       </c>
       <c r="B190" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19232,21 +19240,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19256,10 +19264,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>434763</v>
+        <v>435205</v>
       </c>
       <c r="R190" t="n">
-        <v>6782543</v>
+        <v>6782175</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19286,12 +19294,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -19318,10 +19326,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129996322</v>
+        <v>129996290</v>
       </c>
       <c r="B191" t="n">
-        <v>57737</v>
+        <v>79678</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19329,42 +19337,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>434994</v>
+        <v>434998</v>
       </c>
       <c r="R191" t="n">
-        <v>6782340</v>
+        <v>6782675</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>

--- a/artfynd/A 59104-2025 artfynd.xlsx
+++ b/artfynd/A 59104-2025 artfynd.xlsx
@@ -7232,45 +7232,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129996246</v>
+        <v>129996358</v>
       </c>
       <c r="B68" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434807</v>
+        <v>434760</v>
       </c>
       <c r="R68" t="n">
-        <v>6782563</v>
+        <v>6782538</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7311,6 +7320,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7329,10 +7339,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129996432</v>
+        <v>129996346</v>
       </c>
       <c r="B69" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7340,21 +7350,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7364,10 +7374,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434914</v>
+        <v>435183</v>
       </c>
       <c r="R69" t="n">
-        <v>6782567</v>
+        <v>6782321</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7394,17 +7404,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7431,10 +7436,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129996247</v>
+        <v>129996350</v>
       </c>
       <c r="B70" t="n">
-        <v>79714</v>
+        <v>78853</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7442,21 +7447,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7466,10 +7471,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434888</v>
+        <v>435162</v>
       </c>
       <c r="R70" t="n">
-        <v>6782580</v>
+        <v>6782182</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7496,12 +7501,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7528,10 +7533,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129996274</v>
+        <v>129996441</v>
       </c>
       <c r="B71" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7539,21 +7544,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7563,10 +7568,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435211</v>
+        <v>434998</v>
       </c>
       <c r="R71" t="n">
-        <v>6782225</v>
+        <v>6782688</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7625,10 +7630,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129996380</v>
+        <v>129996319</v>
       </c>
       <c r="B72" t="n">
-        <v>78852</v>
+        <v>57738</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7636,34 +7641,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435050</v>
+        <v>434790</v>
       </c>
       <c r="R72" t="n">
-        <v>6782431</v>
+        <v>6782588</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7690,12 +7703,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7722,10 +7735,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129996234</v>
+        <v>129996459</v>
       </c>
       <c r="B73" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7733,21 +7746,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7757,10 +7770,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>434836</v>
+        <v>435125</v>
       </c>
       <c r="R73" t="n">
-        <v>6782526</v>
+        <v>6782293</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7787,12 +7800,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7819,10 +7832,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129996383</v>
+        <v>129996472</v>
       </c>
       <c r="B74" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7830,21 +7843,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7854,10 +7867,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435009</v>
+        <v>435148</v>
       </c>
       <c r="R74" t="n">
-        <v>6782361</v>
+        <v>6782237</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7916,7 +7929,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129996441</v>
+        <v>129996427</v>
       </c>
       <c r="B75" t="n">
         <v>79095</v>
@@ -7951,10 +7964,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434998</v>
+        <v>434810</v>
       </c>
       <c r="R75" t="n">
-        <v>6782688</v>
+        <v>6782537</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7981,12 +7994,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8013,32 +8026,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129996319</v>
+        <v>129996305</v>
       </c>
       <c r="B76" t="n">
-        <v>57738</v>
+        <v>56931</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8046,7 +8059,7 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -8056,10 +8069,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434790</v>
+        <v>434975</v>
       </c>
       <c r="R76" t="n">
-        <v>6782588</v>
+        <v>6782364</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8086,12 +8099,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8118,53 +8131,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129996305</v>
+        <v>129996246</v>
       </c>
       <c r="B77" t="n">
-        <v>56931</v>
+        <v>79714</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434975</v>
+        <v>434807</v>
       </c>
       <c r="R77" t="n">
-        <v>6782364</v>
+        <v>6782563</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8191,12 +8196,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8223,54 +8228,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129996358</v>
+        <v>129996432</v>
       </c>
       <c r="B78" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434760</v>
+        <v>434914</v>
       </c>
       <c r="R78" t="n">
-        <v>6782538</v>
+        <v>6782567</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8305,13 +8301,17 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8330,10 +8330,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129996459</v>
+        <v>129996247</v>
       </c>
       <c r="B79" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8341,21 +8341,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8365,10 +8365,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435125</v>
+        <v>434888</v>
       </c>
       <c r="R79" t="n">
-        <v>6782293</v>
+        <v>6782580</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8395,12 +8395,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8427,10 +8427,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129996472</v>
+        <v>129996274</v>
       </c>
       <c r="B80" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8438,21 +8438,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8462,10 +8462,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435148</v>
+        <v>435211</v>
       </c>
       <c r="R80" t="n">
-        <v>6782237</v>
+        <v>6782225</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8524,10 +8524,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129996427</v>
+        <v>129996380</v>
       </c>
       <c r="B81" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8535,21 +8535,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8559,10 +8559,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>434810</v>
+        <v>435050</v>
       </c>
       <c r="R81" t="n">
-        <v>6782537</v>
+        <v>6782431</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8589,12 +8589,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8621,10 +8621,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129996346</v>
+        <v>129996234</v>
       </c>
       <c r="B82" t="n">
-        <v>78853</v>
+        <v>79714</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8632,21 +8632,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>435183</v>
+        <v>434836</v>
       </c>
       <c r="R82" t="n">
-        <v>6782321</v>
+        <v>6782526</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8686,12 +8686,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8718,10 +8718,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129996350</v>
+        <v>129996383</v>
       </c>
       <c r="B83" t="n">
-        <v>78853</v>
+        <v>78852</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8729,21 +8729,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8753,10 +8753,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>435162</v>
+        <v>435009</v>
       </c>
       <c r="R83" t="n">
-        <v>6782182</v>
+        <v>6782361</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -12244,10 +12244,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129996348</v>
+        <v>129996271</v>
       </c>
       <c r="B119" t="n">
-        <v>78853</v>
+        <v>79714</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12255,21 +12255,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12279,10 +12279,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>435230</v>
+        <v>435189</v>
       </c>
       <c r="R119" t="n">
-        <v>6782260</v>
+        <v>6782244</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12341,10 +12341,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129996342</v>
+        <v>129996259</v>
       </c>
       <c r="B120" t="n">
-        <v>78853</v>
+        <v>79714</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12352,21 +12352,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12376,10 +12376,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>435104</v>
+        <v>435020</v>
       </c>
       <c r="R120" t="n">
-        <v>6782300</v>
+        <v>6782612</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12438,10 +12438,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129996332</v>
+        <v>129996447</v>
       </c>
       <c r="B121" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12449,21 +12449,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12473,10 +12473,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>434796</v>
+        <v>435039</v>
       </c>
       <c r="R121" t="n">
-        <v>6782579</v>
+        <v>6782658</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12503,12 +12503,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12535,10 +12535,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129996334</v>
+        <v>129996403</v>
       </c>
       <c r="B122" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12546,37 +12546,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>434994</v>
+        <v>435025</v>
       </c>
       <c r="R122" t="n">
-        <v>6782543</v>
+        <v>6782389</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12617,7 +12614,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12636,45 +12632,48 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129996298</v>
+        <v>129996481</v>
       </c>
       <c r="B123" t="n">
-        <v>79685</v>
+        <v>92921</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>435213</v>
+        <v>434976</v>
       </c>
       <c r="R123" t="n">
-        <v>6782254</v>
+        <v>6782376</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12715,6 +12714,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12733,48 +12733,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129996481</v>
+        <v>129996348</v>
       </c>
       <c r="B124" t="n">
-        <v>92921</v>
+        <v>78853</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>434976</v>
+        <v>435230</v>
       </c>
       <c r="R124" t="n">
-        <v>6782376</v>
+        <v>6782260</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12815,7 +12812,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -12834,10 +12830,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129996271</v>
+        <v>129996342</v>
       </c>
       <c r="B125" t="n">
-        <v>79714</v>
+        <v>78853</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12845,21 +12841,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12869,10 +12865,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>435189</v>
+        <v>435104</v>
       </c>
       <c r="R125" t="n">
-        <v>6782244</v>
+        <v>6782300</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12931,10 +12927,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129996259</v>
+        <v>129996332</v>
       </c>
       <c r="B126" t="n">
-        <v>79714</v>
+        <v>78853</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12942,21 +12938,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12966,10 +12962,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>435020</v>
+        <v>434796</v>
       </c>
       <c r="R126" t="n">
-        <v>6782612</v>
+        <v>6782579</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12996,12 +12992,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13028,10 +13024,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129996447</v>
+        <v>129996334</v>
       </c>
       <c r="B127" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13039,34 +13035,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>435039</v>
+        <v>434994</v>
       </c>
       <c r="R127" t="n">
-        <v>6782658</v>
+        <v>6782543</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13093,12 +13092,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13107,6 +13106,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13125,10 +13125,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129996403</v>
+        <v>129996298</v>
       </c>
       <c r="B128" t="n">
-        <v>79095</v>
+        <v>79685</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13136,21 +13136,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13160,10 +13160,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>435025</v>
+        <v>435213</v>
       </c>
       <c r="R128" t="n">
-        <v>6782389</v>
+        <v>6782254</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13190,12 +13190,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13222,10 +13222,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129996279</v>
+        <v>129996476</v>
       </c>
       <c r="B129" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13233,21 +13233,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13257,10 +13257,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>435130</v>
+        <v>435079</v>
       </c>
       <c r="R129" t="n">
-        <v>6782186</v>
+        <v>6782284</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13293,6 +13293,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13319,10 +13324,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129996476</v>
+        <v>129996240</v>
       </c>
       <c r="B130" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13330,21 +13335,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13354,10 +13359,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>435079</v>
+        <v>434765</v>
       </c>
       <c r="R130" t="n">
-        <v>6782284</v>
+        <v>6782566</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13384,17 +13389,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13421,10 +13421,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129996240</v>
+        <v>129996370</v>
       </c>
       <c r="B131" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13432,21 +13432,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13456,10 +13456,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>434765</v>
+        <v>434902</v>
       </c>
       <c r="R131" t="n">
-        <v>6782566</v>
+        <v>6782754</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13518,10 +13518,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129996370</v>
+        <v>129996238</v>
       </c>
       <c r="B132" t="n">
-        <v>78852</v>
+        <v>79714</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13529,21 +13529,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>434902</v>
+        <v>434763</v>
       </c>
       <c r="R132" t="n">
-        <v>6782754</v>
+        <v>6782555</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13615,7 +13615,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129996238</v>
+        <v>129996215</v>
       </c>
       <c r="B133" t="n">
         <v>79714</v>
@@ -13650,10 +13650,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>434763</v>
+        <v>434939</v>
       </c>
       <c r="R133" t="n">
-        <v>6782555</v>
+        <v>6782693</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13712,7 +13712,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129996215</v>
+        <v>129996279</v>
       </c>
       <c r="B134" t="n">
         <v>79714</v>
@@ -13747,10 +13747,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>434939</v>
+        <v>435130</v>
       </c>
       <c r="R134" t="n">
-        <v>6782693</v>
+        <v>6782186</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13777,12 +13777,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -13906,10 +13906,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129996454</v>
+        <v>129996239</v>
       </c>
       <c r="B136" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13917,21 +13917,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13941,10 +13941,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>435024</v>
+        <v>434775</v>
       </c>
       <c r="R136" t="n">
-        <v>6782432</v>
+        <v>6782566</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13971,12 +13971,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14003,10 +14003,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129996266</v>
+        <v>129996453</v>
       </c>
       <c r="B137" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14014,21 +14014,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14038,10 +14038,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>434994</v>
+        <v>435011</v>
       </c>
       <c r="R137" t="n">
-        <v>6782358</v>
+        <v>6782456</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14074,6 +14074,11 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14100,7 +14105,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129996239</v>
+        <v>129996270</v>
       </c>
       <c r="B138" t="n">
         <v>79714</v>
@@ -14135,10 +14140,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>434775</v>
+        <v>435158</v>
       </c>
       <c r="R138" t="n">
-        <v>6782566</v>
+        <v>6782353</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14165,12 +14170,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14197,7 +14202,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129996453</v>
+        <v>129996405</v>
       </c>
       <c r="B139" t="n">
         <v>79095</v>
@@ -14232,10 +14237,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>435011</v>
+        <v>435097</v>
       </c>
       <c r="R139" t="n">
-        <v>6782456</v>
+        <v>6782414</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14262,17 +14267,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14299,10 +14299,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129996270</v>
+        <v>129996388</v>
       </c>
       <c r="B140" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14310,21 +14310,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14334,10 +14334,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>435158</v>
+        <v>435210</v>
       </c>
       <c r="R140" t="n">
-        <v>6782353</v>
+        <v>6782209</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14396,10 +14396,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129996405</v>
+        <v>129996369</v>
       </c>
       <c r="B141" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14407,21 +14407,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14431,10 +14431,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>435097</v>
+        <v>434939</v>
       </c>
       <c r="R141" t="n">
-        <v>6782414</v>
+        <v>6782721</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14493,10 +14493,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129996388</v>
+        <v>129996454</v>
       </c>
       <c r="B142" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14504,21 +14504,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14528,10 +14528,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>435210</v>
+        <v>435024</v>
       </c>
       <c r="R142" t="n">
-        <v>6782209</v>
+        <v>6782432</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14590,10 +14590,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129996369</v>
+        <v>129996266</v>
       </c>
       <c r="B143" t="n">
-        <v>78852</v>
+        <v>79714</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14601,21 +14601,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14625,10 +14625,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>434939</v>
+        <v>434994</v>
       </c>
       <c r="R143" t="n">
-        <v>6782721</v>
+        <v>6782358</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14655,12 +14655,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14986,45 +14986,54 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129996289</v>
+        <v>129996361</v>
       </c>
       <c r="B147" t="n">
-        <v>79685</v>
+        <v>8451</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>434909</v>
+        <v>435003</v>
       </c>
       <c r="R147" t="n">
-        <v>6782588</v>
+        <v>6782399</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15051,12 +15060,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15065,6 +15074,7 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -15480,54 +15490,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129996361</v>
+        <v>129996289</v>
       </c>
       <c r="B152" t="n">
-        <v>8451</v>
+        <v>79685</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>435003</v>
+        <v>434909</v>
       </c>
       <c r="R152" t="n">
-        <v>6782399</v>
+        <v>6782588</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15554,12 +15555,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15568,7 +15569,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -16279,45 +16279,53 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129996470</v>
+        <v>129996304</v>
       </c>
       <c r="B160" t="n">
-        <v>79095</v>
+        <v>56931</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>435154</v>
+        <v>435028</v>
       </c>
       <c r="R160" t="n">
-        <v>6782190</v>
+        <v>6782608</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16376,7 +16384,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129996440</v>
+        <v>129996470</v>
       </c>
       <c r="B161" t="n">
         <v>79095</v>
@@ -16411,10 +16419,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>434996</v>
+        <v>435154</v>
       </c>
       <c r="R161" t="n">
-        <v>6782623</v>
+        <v>6782190</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16473,53 +16481,45 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129996304</v>
+        <v>129996440</v>
       </c>
       <c r="B162" t="n">
-        <v>56931</v>
+        <v>79095</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>435028</v>
+        <v>434996</v>
       </c>
       <c r="R162" t="n">
-        <v>6782608</v>
+        <v>6782623</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>

--- a/artfynd/A 59104-2025 artfynd.xlsx
+++ b/artfynd/A 59104-2025 artfynd.xlsx
@@ -4546,10 +4546,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129996221</v>
+        <v>129996320</v>
       </c>
       <c r="B41" t="n">
-        <v>79714</v>
+        <v>57738</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4557,34 +4557,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434873</v>
+        <v>435015</v>
       </c>
       <c r="R41" t="n">
-        <v>6782710</v>
+        <v>6782457</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4611,12 +4619,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4643,7 +4651,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129996436</v>
+        <v>129996450</v>
       </c>
       <c r="B42" t="n">
         <v>79095</v>
@@ -4672,16 +4680,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434988</v>
+        <v>435061</v>
       </c>
       <c r="R42" t="n">
-        <v>6782549</v>
+        <v>6782474</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4708,17 +4719,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4727,6 +4738,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4745,45 +4757,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129996283</v>
+        <v>129996360</v>
       </c>
       <c r="B43" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435090</v>
+        <v>435016</v>
       </c>
       <c r="R43" t="n">
-        <v>6782256</v>
+        <v>6782447</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4824,6 +4845,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4842,10 +4864,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129996437</v>
+        <v>129996288</v>
       </c>
       <c r="B44" t="n">
-        <v>79095</v>
+        <v>79685</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4853,21 +4875,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4877,10 +4899,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434995</v>
+        <v>434753</v>
       </c>
       <c r="R44" t="n">
-        <v>6782563</v>
+        <v>6782550</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4939,10 +4961,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129996461</v>
+        <v>129996340</v>
       </c>
       <c r="B45" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4950,21 +4972,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4974,10 +4996,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435138</v>
+        <v>434965</v>
       </c>
       <c r="R45" t="n">
-        <v>6782383</v>
+        <v>6782389</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5010,11 +5032,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5041,10 +5058,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129996320</v>
+        <v>129996221</v>
       </c>
       <c r="B46" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5052,42 +5069,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435015</v>
+        <v>434873</v>
       </c>
       <c r="R46" t="n">
-        <v>6782457</v>
+        <v>6782710</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5114,12 +5123,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5146,10 +5155,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129996347</v>
+        <v>129996436</v>
       </c>
       <c r="B47" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5157,21 +5166,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5181,10 +5190,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435217</v>
+        <v>434988</v>
       </c>
       <c r="R47" t="n">
-        <v>6782258</v>
+        <v>6782549</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5211,12 +5220,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5243,10 +5257,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129996297</v>
+        <v>129996283</v>
       </c>
       <c r="B48" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5254,21 +5268,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5278,10 +5292,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435187</v>
+        <v>435090</v>
       </c>
       <c r="R48" t="n">
-        <v>6782242</v>
+        <v>6782256</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5340,10 +5354,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129996288</v>
+        <v>129996437</v>
       </c>
       <c r="B49" t="n">
-        <v>79685</v>
+        <v>79095</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5351,21 +5365,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5375,10 +5389,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434753</v>
+        <v>434995</v>
       </c>
       <c r="R49" t="n">
-        <v>6782550</v>
+        <v>6782563</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5437,10 +5451,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129996340</v>
+        <v>129996461</v>
       </c>
       <c r="B50" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5448,21 +5462,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5472,10 +5486,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434965</v>
+        <v>435138</v>
       </c>
       <c r="R50" t="n">
-        <v>6782389</v>
+        <v>6782383</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5508,6 +5522,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5534,10 +5553,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129996450</v>
+        <v>129996284</v>
       </c>
       <c r="B51" t="n">
-        <v>79095</v>
+        <v>79685</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5545,37 +5564,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435061</v>
+        <v>434655</v>
       </c>
       <c r="R51" t="n">
-        <v>6782474</v>
+        <v>6782666</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5602,17 +5618,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5621,7 +5632,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5640,54 +5650,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129996360</v>
+        <v>129996347</v>
       </c>
       <c r="B52" t="n">
-        <v>8451</v>
+        <v>78853</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435016</v>
+        <v>435217</v>
       </c>
       <c r="R52" t="n">
-        <v>6782447</v>
+        <v>6782258</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5728,7 +5729,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5747,7 +5747,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129996284</v>
+        <v>129996297</v>
       </c>
       <c r="B53" t="n">
         <v>79685</v>
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434655</v>
+        <v>435187</v>
       </c>
       <c r="R53" t="n">
-        <v>6782666</v>
+        <v>6782242</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5812,12 +5812,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7232,54 +7232,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129996358</v>
+        <v>129996246</v>
       </c>
       <c r="B68" t="n">
-        <v>8451</v>
+        <v>79714</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434760</v>
+        <v>434807</v>
       </c>
       <c r="R68" t="n">
-        <v>6782538</v>
+        <v>6782563</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7320,7 +7311,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7339,10 +7329,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129996346</v>
+        <v>129996432</v>
       </c>
       <c r="B69" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7350,21 +7340,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7374,10 +7364,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435183</v>
+        <v>434914</v>
       </c>
       <c r="R69" t="n">
-        <v>6782321</v>
+        <v>6782567</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7404,12 +7394,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7436,10 +7431,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129996350</v>
+        <v>129996247</v>
       </c>
       <c r="B70" t="n">
-        <v>78853</v>
+        <v>79714</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7447,21 +7442,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7471,10 +7466,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435162</v>
+        <v>434888</v>
       </c>
       <c r="R70" t="n">
-        <v>6782182</v>
+        <v>6782580</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7501,12 +7496,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7533,10 +7528,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129996441</v>
+        <v>129996274</v>
       </c>
       <c r="B71" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7544,21 +7539,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7568,10 +7563,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>434998</v>
+        <v>435211</v>
       </c>
       <c r="R71" t="n">
-        <v>6782688</v>
+        <v>6782225</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7630,10 +7625,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129996319</v>
+        <v>129996380</v>
       </c>
       <c r="B72" t="n">
-        <v>57738</v>
+        <v>78852</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7641,42 +7636,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>434790</v>
+        <v>435050</v>
       </c>
       <c r="R72" t="n">
-        <v>6782588</v>
+        <v>6782431</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7703,12 +7690,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7735,10 +7722,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129996459</v>
+        <v>129996234</v>
       </c>
       <c r="B73" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7746,21 +7733,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7770,10 +7757,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>435125</v>
+        <v>434836</v>
       </c>
       <c r="R73" t="n">
-        <v>6782293</v>
+        <v>6782526</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7800,12 +7787,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7832,10 +7819,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129996472</v>
+        <v>129996383</v>
       </c>
       <c r="B74" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7843,21 +7830,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7867,10 +7854,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435148</v>
+        <v>435009</v>
       </c>
       <c r="R74" t="n">
-        <v>6782237</v>
+        <v>6782361</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7929,7 +7916,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129996427</v>
+        <v>129996441</v>
       </c>
       <c r="B75" t="n">
         <v>79095</v>
@@ -7964,10 +7951,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434810</v>
+        <v>434998</v>
       </c>
       <c r="R75" t="n">
-        <v>6782537</v>
+        <v>6782688</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7994,12 +7981,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8026,32 +8013,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129996305</v>
+        <v>129996319</v>
       </c>
       <c r="B76" t="n">
-        <v>56931</v>
+        <v>57738</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8059,7 +8046,7 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -8069,10 +8056,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434975</v>
+        <v>434790</v>
       </c>
       <c r="R76" t="n">
-        <v>6782364</v>
+        <v>6782588</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8099,12 +8086,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8131,45 +8118,53 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129996246</v>
+        <v>129996305</v>
       </c>
       <c r="B77" t="n">
-        <v>79714</v>
+        <v>56931</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434807</v>
+        <v>434975</v>
       </c>
       <c r="R77" t="n">
-        <v>6782563</v>
+        <v>6782364</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8196,12 +8191,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8228,45 +8223,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129996432</v>
+        <v>129996358</v>
       </c>
       <c r="B78" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434914</v>
+        <v>434760</v>
       </c>
       <c r="R78" t="n">
-        <v>6782567</v>
+        <v>6782538</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8301,17 +8305,13 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8330,10 +8330,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129996247</v>
+        <v>129996459</v>
       </c>
       <c r="B79" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8341,21 +8341,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8365,10 +8365,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>434888</v>
+        <v>435125</v>
       </c>
       <c r="R79" t="n">
-        <v>6782580</v>
+        <v>6782293</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8395,12 +8395,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8427,10 +8427,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129996274</v>
+        <v>129996472</v>
       </c>
       <c r="B80" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8438,21 +8438,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8462,10 +8462,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435211</v>
+        <v>435148</v>
       </c>
       <c r="R80" t="n">
-        <v>6782225</v>
+        <v>6782237</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8524,10 +8524,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129996380</v>
+        <v>129996427</v>
       </c>
       <c r="B81" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8535,21 +8535,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8559,10 +8559,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435050</v>
+        <v>434810</v>
       </c>
       <c r="R81" t="n">
-        <v>6782431</v>
+        <v>6782537</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8589,12 +8589,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8621,10 +8621,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129996234</v>
+        <v>129996346</v>
       </c>
       <c r="B82" t="n">
-        <v>79714</v>
+        <v>78853</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8632,21 +8632,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>434836</v>
+        <v>435183</v>
       </c>
       <c r="R82" t="n">
-        <v>6782526</v>
+        <v>6782321</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8686,12 +8686,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8718,10 +8718,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129996383</v>
+        <v>129996350</v>
       </c>
       <c r="B83" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8729,21 +8729,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8753,10 +8753,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>435009</v>
+        <v>435162</v>
       </c>
       <c r="R83" t="n">
-        <v>6782361</v>
+        <v>6782182</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8815,10 +8815,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129996229</v>
+        <v>129996439</v>
       </c>
       <c r="B84" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8826,21 +8826,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8850,10 +8850,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434658</v>
+        <v>435093</v>
       </c>
       <c r="R84" t="n">
-        <v>6782564</v>
+        <v>6782501</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8880,12 +8880,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8912,10 +8912,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129996387</v>
+        <v>129996406</v>
       </c>
       <c r="B85" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8923,21 +8923,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8947,10 +8947,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>435183</v>
+        <v>434821</v>
       </c>
       <c r="R85" t="n">
-        <v>6782321</v>
+        <v>6782740</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8977,12 +8977,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9009,7 +9009,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129996439</v>
+        <v>129996462</v>
       </c>
       <c r="B86" t="n">
         <v>79095</v>
@@ -9044,10 +9044,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>435093</v>
+        <v>435151</v>
       </c>
       <c r="R86" t="n">
-        <v>6782501</v>
+        <v>6782374</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9106,7 +9106,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129996406</v>
+        <v>129996438</v>
       </c>
       <c r="B87" t="n">
         <v>79095</v>
@@ -9141,10 +9141,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434821</v>
+        <v>435115</v>
       </c>
       <c r="R87" t="n">
-        <v>6782740</v>
+        <v>6782481</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9171,12 +9171,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9203,10 +9203,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129996462</v>
+        <v>129996253</v>
       </c>
       <c r="B88" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9214,21 +9214,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9238,10 +9238,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>435151</v>
+        <v>435109</v>
       </c>
       <c r="R88" t="n">
-        <v>6782374</v>
+        <v>6782484</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9300,10 +9300,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129996438</v>
+        <v>129996230</v>
       </c>
       <c r="B89" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9311,21 +9311,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9335,10 +9335,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>435115</v>
+        <v>434674</v>
       </c>
       <c r="R89" t="n">
-        <v>6782481</v>
+        <v>6782596</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9365,12 +9365,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9397,7 +9397,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129996253</v>
+        <v>129996255</v>
       </c>
       <c r="B90" t="n">
         <v>79714</v>
@@ -9432,10 +9432,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>435109</v>
+        <v>434998</v>
       </c>
       <c r="R90" t="n">
-        <v>6782484</v>
+        <v>6782675</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9494,7 +9494,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129996230</v>
+        <v>129996229</v>
       </c>
       <c r="B91" t="n">
         <v>79714</v>
@@ -9529,10 +9529,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>434674</v>
+        <v>434658</v>
       </c>
       <c r="R91" t="n">
-        <v>6782596</v>
+        <v>6782564</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9591,10 +9591,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129996255</v>
+        <v>129996387</v>
       </c>
       <c r="B92" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9602,21 +9602,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>434998</v>
+        <v>435183</v>
       </c>
       <c r="R92" t="n">
-        <v>6782675</v>
+        <v>6782321</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -13222,10 +13222,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129996476</v>
+        <v>129996279</v>
       </c>
       <c r="B129" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13233,21 +13233,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13257,10 +13257,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>435079</v>
+        <v>435130</v>
       </c>
       <c r="R129" t="n">
-        <v>6782284</v>
+        <v>6782186</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13293,11 +13293,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13324,10 +13319,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129996240</v>
+        <v>129996476</v>
       </c>
       <c r="B130" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13335,21 +13330,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13359,10 +13354,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>434765</v>
+        <v>435079</v>
       </c>
       <c r="R130" t="n">
-        <v>6782566</v>
+        <v>6782284</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13389,12 +13384,17 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13421,10 +13421,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129996370</v>
+        <v>129996240</v>
       </c>
       <c r="B131" t="n">
-        <v>78852</v>
+        <v>79714</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13432,21 +13432,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13456,10 +13456,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>434902</v>
+        <v>434765</v>
       </c>
       <c r="R131" t="n">
-        <v>6782754</v>
+        <v>6782566</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13518,10 +13518,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129996238</v>
+        <v>129996370</v>
       </c>
       <c r="B132" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13529,21 +13529,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>434763</v>
+        <v>434902</v>
       </c>
       <c r="R132" t="n">
-        <v>6782555</v>
+        <v>6782754</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13615,7 +13615,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129996215</v>
+        <v>129996238</v>
       </c>
       <c r="B133" t="n">
         <v>79714</v>
@@ -13650,10 +13650,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>434939</v>
+        <v>434763</v>
       </c>
       <c r="R133" t="n">
-        <v>6782693</v>
+        <v>6782555</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13712,7 +13712,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129996279</v>
+        <v>129996215</v>
       </c>
       <c r="B134" t="n">
         <v>79714</v>
@@ -13747,10 +13747,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>435130</v>
+        <v>434939</v>
       </c>
       <c r="R134" t="n">
-        <v>6782186</v>
+        <v>6782693</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13777,12 +13777,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14986,54 +14986,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129996361</v>
+        <v>129996289</v>
       </c>
       <c r="B147" t="n">
-        <v>8451</v>
+        <v>79685</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>435003</v>
+        <v>434909</v>
       </c>
       <c r="R147" t="n">
-        <v>6782399</v>
+        <v>6782588</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15060,12 +15051,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15074,7 +15065,6 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -15490,45 +15480,54 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129996289</v>
+        <v>129996361</v>
       </c>
       <c r="B152" t="n">
-        <v>79685</v>
+        <v>8451</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>434909</v>
+        <v>435003</v>
       </c>
       <c r="R152" t="n">
-        <v>6782588</v>
+        <v>6782399</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15555,12 +15554,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15569,6 +15568,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -19027,10 +19027,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129996290</v>
+        <v>129996322</v>
       </c>
       <c r="B188" t="n">
-        <v>79685</v>
+        <v>57738</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19038,34 +19038,42 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>434998</v>
+        <v>434994</v>
       </c>
       <c r="R188" t="n">
-        <v>6782675</v>
+        <v>6782340</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19124,10 +19132,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129996322</v>
+        <v>129996252</v>
       </c>
       <c r="B189" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19135,42 +19143,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>434994</v>
+        <v>435114</v>
       </c>
       <c r="R189" t="n">
-        <v>6782340</v>
+        <v>6782479</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19229,7 +19229,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129996252</v>
+        <v>129996277</v>
       </c>
       <c r="B190" t="n">
         <v>79714</v>
@@ -19264,10 +19264,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>435114</v>
+        <v>435153</v>
       </c>
       <c r="R190" t="n">
-        <v>6782479</v>
+        <v>6782169</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19326,10 +19326,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129996277</v>
+        <v>129996290</v>
       </c>
       <c r="B191" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19337,21 +19337,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19361,10 +19361,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>435153</v>
+        <v>434998</v>
       </c>
       <c r="R191" t="n">
-        <v>6782169</v>
+        <v>6782675</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19621,10 +19621,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129996244</v>
+        <v>129996376</v>
       </c>
       <c r="B194" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19632,21 +19632,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19656,10 +19656,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>434789</v>
+        <v>435039</v>
       </c>
       <c r="R194" t="n">
-        <v>6782590</v>
+        <v>6782675</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19686,12 +19686,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -19718,7 +19718,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129996216</v>
+        <v>129996263</v>
       </c>
       <c r="B195" t="n">
         <v>79714</v>
@@ -19753,10 +19753,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>434928</v>
+        <v>435076</v>
       </c>
       <c r="R195" t="n">
-        <v>6782707</v>
+        <v>6782532</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -19783,12 +19783,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -19815,10 +19815,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129996376</v>
+        <v>129996425</v>
       </c>
       <c r="B196" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19826,21 +19826,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -19850,10 +19850,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>435039</v>
+        <v>434836</v>
       </c>
       <c r="R196" t="n">
-        <v>6782675</v>
+        <v>6782524</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -19880,12 +19880,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -19912,7 +19912,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129996263</v>
+        <v>129996268</v>
       </c>
       <c r="B197" t="n">
         <v>79714</v>
@@ -19947,10 +19947,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>435076</v>
+        <v>435103</v>
       </c>
       <c r="R197" t="n">
-        <v>6782532</v>
+        <v>6782305</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20009,10 +20009,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129996425</v>
+        <v>129996244</v>
       </c>
       <c r="B198" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20020,21 +20020,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20044,10 +20044,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>434836</v>
+        <v>434789</v>
       </c>
       <c r="R198" t="n">
-        <v>6782524</v>
+        <v>6782590</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20106,7 +20106,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129996268</v>
+        <v>129996216</v>
       </c>
       <c r="B199" t="n">
         <v>79714</v>
@@ -20141,10 +20141,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>435103</v>
+        <v>434928</v>
       </c>
       <c r="R199" t="n">
-        <v>6782305</v>
+        <v>6782707</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20171,12 +20171,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -20397,10 +20397,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129996471</v>
+        <v>129996325</v>
       </c>
       <c r="B202" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20408,34 +20408,42 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>435126</v>
+        <v>434755</v>
       </c>
       <c r="R202" t="n">
-        <v>6782203</v>
+        <v>6782589</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20462,12 +20470,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -20494,54 +20502,45 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129996364</v>
+        <v>129996471</v>
       </c>
       <c r="B203" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>435098</v>
+        <v>435126</v>
       </c>
       <c r="R203" t="n">
-        <v>6782306</v>
+        <v>6782203</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20582,7 +20581,6 @@
       <c r="AE203" t="b">
         <v>0</v>
       </c>
-      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
@@ -20698,40 +20696,41 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129996325</v>
+        <v>129996364</v>
       </c>
       <c r="B205" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N205" t="inlineStr"/>
@@ -20741,10 +20740,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>434755</v>
+        <v>435098</v>
       </c>
       <c r="R205" t="n">
-        <v>6782589</v>
+        <v>6782306</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -20771,12 +20770,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -20785,6 +20784,7 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
+      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59104-2025 artfynd.xlsx
+++ b/artfynd/A 59104-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129996362</v>
+        <v>129996426</v>
       </c>
       <c r="B2" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434988</v>
+        <v>434834</v>
       </c>
       <c r="R2" t="n">
-        <v>6782383</v>
+        <v>6782525</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,7 +775,7 @@
         <v>129996213</v>
       </c>
       <c r="B3" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +885,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129996426</v>
+        <v>129996423</v>
       </c>
       <c r="B4" t="n">
         <v>79095</v>
@@ -930,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434834</v>
+        <v>434722</v>
       </c>
       <c r="R4" t="n">
-        <v>6782525</v>
+        <v>6782572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129996281</v>
+        <v>129996420</v>
       </c>
       <c r="B5" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1027,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435132</v>
+        <v>434663</v>
       </c>
       <c r="R5" t="n">
-        <v>6782205</v>
+        <v>6782668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,12 +1047,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129996231</v>
+        <v>129996435</v>
       </c>
       <c r="B6" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434855</v>
+        <v>434970</v>
       </c>
       <c r="R6" t="n">
-        <v>6782501</v>
+        <v>6782543</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1380,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129996323</v>
+        <v>129996483</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>78102</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,42 +1381,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435142</v>
+        <v>434752</v>
       </c>
       <c r="R9" t="n">
-        <v>6782181</v>
+        <v>6782544</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1453,12 +1435,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1485,45 +1467,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129996423</v>
+        <v>129996482</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>92923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434722</v>
+        <v>435094</v>
       </c>
       <c r="R10" t="n">
-        <v>6782572</v>
+        <v>6782249</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1550,12 +1535,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1564,6 +1549,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1582,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129996420</v>
+        <v>129996281</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1617,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434663</v>
+        <v>435132</v>
       </c>
       <c r="R11" t="n">
-        <v>6782668</v>
+        <v>6782205</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1647,12 +1633,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1679,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129996435</v>
+        <v>129996231</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1690,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1714,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434970</v>
+        <v>434855</v>
       </c>
       <c r="R12" t="n">
-        <v>6782543</v>
+        <v>6782501</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129996328</v>
+        <v>129996323</v>
       </c>
       <c r="B13" t="n">
-        <v>78853</v>
+        <v>57738</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1787,34 +1773,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434942</v>
+        <v>435142</v>
       </c>
       <c r="R13" t="n">
-        <v>6782720</v>
+        <v>6782181</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1841,12 +1835,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1873,45 +1867,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129996292</v>
+        <v>129996362</v>
       </c>
       <c r="B14" t="n">
-        <v>79685</v>
+        <v>8451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435018</v>
+        <v>434988</v>
       </c>
       <c r="R14" t="n">
-        <v>6782662</v>
+        <v>6782383</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,6 +1955,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1970,7 +1974,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129996344</v>
+        <v>129996328</v>
       </c>
       <c r="B15" t="n">
         <v>78853</v>
@@ -2005,10 +2009,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435157</v>
+        <v>434942</v>
       </c>
       <c r="R15" t="n">
-        <v>6782371</v>
+        <v>6782720</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2035,12 +2039,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2067,48 +2071,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129996482</v>
+        <v>129996292</v>
       </c>
       <c r="B16" t="n">
-        <v>92921</v>
+        <v>79685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435094</v>
+        <v>435018</v>
       </c>
       <c r="R16" t="n">
-        <v>6782249</v>
+        <v>6782662</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2149,7 +2150,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2168,10 +2168,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129996483</v>
+        <v>129996344</v>
       </c>
       <c r="B17" t="n">
-        <v>78102</v>
+        <v>78853</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434752</v>
+        <v>435157</v>
       </c>
       <c r="R17" t="n">
-        <v>6782544</v>
+        <v>6782371</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3138,10 +3138,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129996226</v>
+        <v>129996324</v>
       </c>
       <c r="B27" t="n">
-        <v>79714</v>
+        <v>57738</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3149,34 +3149,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434636</v>
+        <v>435143</v>
       </c>
       <c r="R27" t="n">
-        <v>6782611</v>
+        <v>6782303</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3203,12 +3211,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3235,7 +3243,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129996227</v>
+        <v>129996226</v>
       </c>
       <c r="B28" t="n">
         <v>79714</v>
@@ -3270,10 +3278,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434657</v>
+        <v>434636</v>
       </c>
       <c r="R28" t="n">
-        <v>6782585</v>
+        <v>6782611</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3332,10 +3340,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129996444</v>
+        <v>129996227</v>
       </c>
       <c r="B29" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3343,21 +3351,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3367,10 +3375,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435010</v>
+        <v>434657</v>
       </c>
       <c r="R29" t="n">
-        <v>6782685</v>
+        <v>6782585</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3397,12 +3405,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3429,10 +3437,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129996371</v>
+        <v>129996214</v>
       </c>
       <c r="B30" t="n">
-        <v>78852</v>
+        <v>79714</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3440,21 +3448,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3464,10 +3472,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434852</v>
+        <v>435028</v>
       </c>
       <c r="R30" t="n">
-        <v>6782499</v>
+        <v>6782399</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3526,10 +3534,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129996324</v>
+        <v>129996371</v>
       </c>
       <c r="B31" t="n">
-        <v>57738</v>
+        <v>78852</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3537,42 +3545,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435143</v>
+        <v>434852</v>
       </c>
       <c r="R31" t="n">
-        <v>6782303</v>
+        <v>6782499</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3599,12 +3599,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3631,10 +3631,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129996214</v>
+        <v>129996311</v>
       </c>
       <c r="B32" t="n">
-        <v>79714</v>
+        <v>57900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3642,34 +3642,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435028</v>
+        <v>435065</v>
       </c>
       <c r="R32" t="n">
-        <v>6782399</v>
+        <v>6782516</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,12 +3704,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3728,45 +3736,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129996463</v>
+        <v>129996353</v>
       </c>
       <c r="B33" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435172</v>
+        <v>434838</v>
       </c>
       <c r="R33" t="n">
-        <v>6782321</v>
+        <v>6782905</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,12 +3810,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3807,6 +3824,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3825,40 +3843,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129996311</v>
+        <v>129996359</v>
       </c>
       <c r="B34" t="n">
-        <v>57900</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3868,10 +3887,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435065</v>
+        <v>434911</v>
       </c>
       <c r="R34" t="n">
-        <v>6782516</v>
+        <v>6782571</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3898,12 +3917,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3912,6 +3931,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3930,54 +3950,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129996359</v>
+        <v>129996295</v>
       </c>
       <c r="B35" t="n">
-        <v>8451</v>
+        <v>79685</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434911</v>
+        <v>434994</v>
       </c>
       <c r="R35" t="n">
-        <v>6782571</v>
+        <v>6782360</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4004,12 +4015,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4018,7 +4029,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4037,54 +4047,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129996353</v>
+        <v>129996463</v>
       </c>
       <c r="B36" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>434838</v>
+        <v>435172</v>
       </c>
       <c r="R36" t="n">
-        <v>6782905</v>
+        <v>6782321</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4111,12 +4112,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4125,7 +4126,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4144,10 +4144,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129996295</v>
+        <v>129996444</v>
       </c>
       <c r="B37" t="n">
-        <v>79685</v>
+        <v>79095</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4155,21 +4155,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434994</v>
+        <v>435010</v>
       </c>
       <c r="R37" t="n">
-        <v>6782360</v>
+        <v>6782685</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
         <v>129996480</v>
       </c>
       <c r="B38" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4342,45 +4342,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129996222</v>
+        <v>129996365</v>
       </c>
       <c r="B39" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434675</v>
+        <v>435171</v>
       </c>
       <c r="R39" t="n">
-        <v>6782699</v>
+        <v>6782319</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4407,12 +4416,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4421,6 +4430,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4439,54 +4449,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129996365</v>
+        <v>129996222</v>
       </c>
       <c r="B40" t="n">
-        <v>8451</v>
+        <v>79714</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435171</v>
+        <v>434675</v>
       </c>
       <c r="R40" t="n">
-        <v>6782319</v>
+        <v>6782699</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4513,12 +4514,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4527,7 +4528,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4546,10 +4546,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129996320</v>
+        <v>129996221</v>
       </c>
       <c r="B41" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4557,42 +4557,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435015</v>
+        <v>434873</v>
       </c>
       <c r="R41" t="n">
-        <v>6782457</v>
+        <v>6782710</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4619,12 +4611,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4651,10 +4643,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129996450</v>
+        <v>129996283</v>
       </c>
       <c r="B42" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4662,37 +4654,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435061</v>
+        <v>435090</v>
       </c>
       <c r="R42" t="n">
-        <v>6782474</v>
+        <v>6782256</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4727,18 +4716,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4757,41 +4740,40 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129996360</v>
+        <v>129996320</v>
       </c>
       <c r="B43" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -4801,10 +4783,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435016</v>
+        <v>435015</v>
       </c>
       <c r="R43" t="n">
-        <v>6782447</v>
+        <v>6782457</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4845,7 +4827,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4864,45 +4845,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129996288</v>
+        <v>129996360</v>
       </c>
       <c r="B44" t="n">
-        <v>79685</v>
+        <v>8451</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434753</v>
+        <v>435016</v>
       </c>
       <c r="R44" t="n">
-        <v>6782550</v>
+        <v>6782447</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4929,12 +4919,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4943,6 +4933,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4961,10 +4952,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129996340</v>
+        <v>129996284</v>
       </c>
       <c r="B45" t="n">
-        <v>78853</v>
+        <v>79685</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4972,21 +4963,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4996,10 +4987,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434965</v>
+        <v>434655</v>
       </c>
       <c r="R45" t="n">
-        <v>6782389</v>
+        <v>6782666</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5026,12 +5017,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5058,10 +5049,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129996221</v>
+        <v>129996288</v>
       </c>
       <c r="B46" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5069,21 +5060,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5093,10 +5084,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434873</v>
+        <v>434753</v>
       </c>
       <c r="R46" t="n">
-        <v>6782710</v>
+        <v>6782550</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5155,10 +5146,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129996436</v>
+        <v>129996340</v>
       </c>
       <c r="B47" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5166,21 +5157,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5190,10 +5181,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434988</v>
+        <v>434965</v>
       </c>
       <c r="R47" t="n">
-        <v>6782549</v>
+        <v>6782389</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5220,17 +5211,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5257,10 +5243,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129996283</v>
+        <v>129996436</v>
       </c>
       <c r="B48" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5268,21 +5254,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5292,10 +5278,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435090</v>
+        <v>434988</v>
       </c>
       <c r="R48" t="n">
-        <v>6782256</v>
+        <v>6782549</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5322,12 +5308,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5451,7 +5442,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129996461</v>
+        <v>129996450</v>
       </c>
       <c r="B50" t="n">
         <v>79095</v>
@@ -5480,16 +5471,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435138</v>
+        <v>435061</v>
       </c>
       <c r="R50" t="n">
-        <v>6782383</v>
+        <v>6782474</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5526,7 +5520,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5535,6 +5529,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5553,10 +5548,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129996284</v>
+        <v>129996461</v>
       </c>
       <c r="B51" t="n">
-        <v>79685</v>
+        <v>79095</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5564,21 +5559,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5588,10 +5583,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434655</v>
+        <v>435138</v>
       </c>
       <c r="R51" t="n">
-        <v>6782666</v>
+        <v>6782383</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5618,12 +5613,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5844,45 +5844,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129996449</v>
+        <v>129996357</v>
       </c>
       <c r="B54" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435085</v>
+        <v>434753</v>
       </c>
       <c r="R54" t="n">
-        <v>6782555</v>
+        <v>6782547</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5909,12 +5918,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5923,6 +5932,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5941,7 +5951,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129996451</v>
+        <v>129996449</v>
       </c>
       <c r="B55" t="n">
         <v>79095</v>
@@ -5976,10 +5986,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435075</v>
+        <v>435085</v>
       </c>
       <c r="R55" t="n">
-        <v>6782440</v>
+        <v>6782555</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6012,11 +6022,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6043,10 +6048,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129996377</v>
+        <v>129996451</v>
       </c>
       <c r="B56" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6054,21 +6059,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6078,10 +6083,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435023</v>
+        <v>435075</v>
       </c>
       <c r="R56" t="n">
-        <v>6782674</v>
+        <v>6782440</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6114,6 +6119,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6140,10 +6150,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129996232</v>
+        <v>129996419</v>
       </c>
       <c r="B57" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6151,21 +6161,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6175,10 +6185,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434842</v>
+        <v>434680</v>
       </c>
       <c r="R57" t="n">
-        <v>6782513</v>
+        <v>6782695</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6237,10 +6247,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129996223</v>
+        <v>129996404</v>
       </c>
       <c r="B58" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6248,21 +6258,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6272,10 +6282,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>434655</v>
+        <v>435071</v>
       </c>
       <c r="R58" t="n">
-        <v>6782666</v>
+        <v>6782409</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6334,7 +6344,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129996465</v>
+        <v>129996410</v>
       </c>
       <c r="B59" t="n">
         <v>79095</v>
@@ -6369,10 +6379,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435213</v>
+        <v>434858</v>
       </c>
       <c r="R59" t="n">
-        <v>6782176</v>
+        <v>6782793</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6399,17 +6409,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6436,7 +6446,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129996468</v>
+        <v>129996465</v>
       </c>
       <c r="B60" t="n">
         <v>79095</v>
@@ -6471,10 +6481,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435181</v>
+        <v>435213</v>
       </c>
       <c r="R60" t="n">
-        <v>6782175</v>
+        <v>6782176</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6507,6 +6517,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6533,7 +6548,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129996419</v>
+        <v>129996468</v>
       </c>
       <c r="B61" t="n">
         <v>79095</v>
@@ -6568,10 +6583,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434680</v>
+        <v>435181</v>
       </c>
       <c r="R61" t="n">
-        <v>6782695</v>
+        <v>6782175</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6598,12 +6613,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6630,10 +6645,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129996404</v>
+        <v>129996377</v>
       </c>
       <c r="B62" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6641,21 +6656,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6665,10 +6680,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>435071</v>
+        <v>435023</v>
       </c>
       <c r="R62" t="n">
-        <v>6782409</v>
+        <v>6782674</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6695,12 +6710,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6727,10 +6742,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129996410</v>
+        <v>129996232</v>
       </c>
       <c r="B63" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6738,21 +6753,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6762,10 +6777,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>434858</v>
+        <v>434842</v>
       </c>
       <c r="R63" t="n">
-        <v>6782793</v>
+        <v>6782513</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6798,11 +6813,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6829,10 +6839,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129996415</v>
+        <v>129996223</v>
       </c>
       <c r="B64" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6840,21 +6850,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6864,10 +6874,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434822</v>
+        <v>434655</v>
       </c>
       <c r="R64" t="n">
-        <v>6782767</v>
+        <v>6782666</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6900,11 +6910,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6931,54 +6936,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129996357</v>
+        <v>129996415</v>
       </c>
       <c r="B65" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434753</v>
+        <v>434822</v>
       </c>
       <c r="R65" t="n">
-        <v>6782547</v>
+        <v>6782767</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7013,13 +7009,17 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7232,10 +7232,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129996246</v>
+        <v>129996459</v>
       </c>
       <c r="B68" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7243,21 +7243,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7267,10 +7267,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434807</v>
+        <v>435125</v>
       </c>
       <c r="R68" t="n">
-        <v>6782563</v>
+        <v>6782293</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7329,7 +7329,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129996432</v>
+        <v>129996472</v>
       </c>
       <c r="B69" t="n">
         <v>79095</v>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434914</v>
+        <v>435148</v>
       </c>
       <c r="R69" t="n">
-        <v>6782567</v>
+        <v>6782237</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7394,17 +7394,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7431,10 +7426,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129996247</v>
+        <v>129996427</v>
       </c>
       <c r="B70" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7442,21 +7437,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7466,10 +7461,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434888</v>
+        <v>434810</v>
       </c>
       <c r="R70" t="n">
-        <v>6782580</v>
+        <v>6782537</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7528,10 +7523,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129996274</v>
+        <v>129996441</v>
       </c>
       <c r="B71" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7539,21 +7534,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7563,10 +7558,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435211</v>
+        <v>434998</v>
       </c>
       <c r="R71" t="n">
-        <v>6782225</v>
+        <v>6782688</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7625,45 +7620,53 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129996380</v>
+        <v>129996305</v>
       </c>
       <c r="B72" t="n">
-        <v>78852</v>
+        <v>56931</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435050</v>
+        <v>434975</v>
       </c>
       <c r="R72" t="n">
-        <v>6782431</v>
+        <v>6782364</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7722,7 +7725,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129996234</v>
+        <v>129996246</v>
       </c>
       <c r="B73" t="n">
         <v>79714</v>
@@ -7757,10 +7760,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>434836</v>
+        <v>434807</v>
       </c>
       <c r="R73" t="n">
-        <v>6782526</v>
+        <v>6782563</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7819,10 +7822,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129996383</v>
+        <v>129996432</v>
       </c>
       <c r="B74" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7830,21 +7833,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7854,10 +7857,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>435009</v>
+        <v>434914</v>
       </c>
       <c r="R74" t="n">
-        <v>6782361</v>
+        <v>6782567</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7884,12 +7887,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7916,10 +7924,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129996441</v>
+        <v>129996247</v>
       </c>
       <c r="B75" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7927,21 +7935,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7951,10 +7959,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434998</v>
+        <v>434888</v>
       </c>
       <c r="R75" t="n">
-        <v>6782688</v>
+        <v>6782580</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7981,12 +7989,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8013,10 +8021,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129996319</v>
+        <v>129996274</v>
       </c>
       <c r="B76" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8024,42 +8032,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434790</v>
+        <v>435211</v>
       </c>
       <c r="R76" t="n">
-        <v>6782588</v>
+        <v>6782225</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8118,53 +8118,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129996305</v>
+        <v>129996380</v>
       </c>
       <c r="B77" t="n">
-        <v>56931</v>
+        <v>78852</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434975</v>
+        <v>435050</v>
       </c>
       <c r="R77" t="n">
-        <v>6782364</v>
+        <v>6782431</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8223,54 +8215,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129996358</v>
+        <v>129996234</v>
       </c>
       <c r="B78" t="n">
-        <v>8451</v>
+        <v>79714</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434760</v>
+        <v>434836</v>
       </c>
       <c r="R78" t="n">
-        <v>6782538</v>
+        <v>6782526</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8311,7 +8294,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8330,10 +8312,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129996459</v>
+        <v>129996383</v>
       </c>
       <c r="B79" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8341,21 +8323,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8365,10 +8347,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>435125</v>
+        <v>435009</v>
       </c>
       <c r="R79" t="n">
-        <v>6782293</v>
+        <v>6782361</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8427,10 +8409,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129996472</v>
+        <v>129996319</v>
       </c>
       <c r="B80" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8438,34 +8420,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>435148</v>
+        <v>434790</v>
       </c>
       <c r="R80" t="n">
-        <v>6782237</v>
+        <v>6782588</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8492,12 +8482,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8524,45 +8514,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129996427</v>
+        <v>129996358</v>
       </c>
       <c r="B81" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>434810</v>
+        <v>434760</v>
       </c>
       <c r="R81" t="n">
-        <v>6782537</v>
+        <v>6782538</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8603,6 +8602,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8912,7 +8912,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129996406</v>
+        <v>129996462</v>
       </c>
       <c r="B85" t="n">
         <v>79095</v>
@@ -8947,10 +8947,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434821</v>
+        <v>435151</v>
       </c>
       <c r="R85" t="n">
-        <v>6782740</v>
+        <v>6782374</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8977,12 +8977,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9009,7 +9009,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129996462</v>
+        <v>129996438</v>
       </c>
       <c r="B86" t="n">
         <v>79095</v>
@@ -9044,10 +9044,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>435151</v>
+        <v>435115</v>
       </c>
       <c r="R86" t="n">
-        <v>6782374</v>
+        <v>6782481</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9106,10 +9106,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129996438</v>
+        <v>129996352</v>
       </c>
       <c r="B87" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9117,21 +9117,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9141,10 +9141,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>435115</v>
+        <v>435089</v>
       </c>
       <c r="R87" t="n">
-        <v>6782481</v>
+        <v>6782304</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9203,10 +9203,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129996253</v>
+        <v>129996285</v>
       </c>
       <c r="B88" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9214,21 +9214,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9238,10 +9238,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>435109</v>
+        <v>434632</v>
       </c>
       <c r="R88" t="n">
-        <v>6782484</v>
+        <v>6782651</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9268,12 +9268,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9300,10 +9300,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129996230</v>
+        <v>129996296</v>
       </c>
       <c r="B89" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9311,21 +9311,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9335,10 +9335,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>434674</v>
+        <v>435156</v>
       </c>
       <c r="R89" t="n">
-        <v>6782596</v>
+        <v>6782351</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9365,12 +9365,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9397,10 +9397,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129996255</v>
+        <v>129996337</v>
       </c>
       <c r="B90" t="n">
-        <v>79714</v>
+        <v>78853</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9408,21 +9408,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9432,10 +9432,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>434998</v>
+        <v>435057</v>
       </c>
       <c r="R90" t="n">
-        <v>6782675</v>
+        <v>6782494</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9494,10 +9494,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129996229</v>
+        <v>129996333</v>
       </c>
       <c r="B91" t="n">
-        <v>79714</v>
+        <v>78853</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9505,21 +9505,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9529,10 +9529,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>434658</v>
+        <v>434909</v>
       </c>
       <c r="R91" t="n">
-        <v>6782564</v>
+        <v>6782588</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9591,10 +9591,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129996387</v>
+        <v>129996406</v>
       </c>
       <c r="B92" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9602,21 +9602,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>435183</v>
+        <v>434821</v>
       </c>
       <c r="R92" t="n">
-        <v>6782321</v>
+        <v>6782740</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9656,12 +9656,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9688,10 +9688,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129996352</v>
+        <v>129996229</v>
       </c>
       <c r="B93" t="n">
-        <v>78853</v>
+        <v>79714</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9699,21 +9699,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9723,10 +9723,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>435089</v>
+        <v>434658</v>
       </c>
       <c r="R93" t="n">
-        <v>6782304</v>
+        <v>6782564</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9753,12 +9753,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9785,10 +9785,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129996285</v>
+        <v>129996253</v>
       </c>
       <c r="B94" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9796,21 +9796,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9820,10 +9820,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>434632</v>
+        <v>435109</v>
       </c>
       <c r="R94" t="n">
-        <v>6782651</v>
+        <v>6782484</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9850,12 +9850,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9882,10 +9882,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129996296</v>
+        <v>129996387</v>
       </c>
       <c r="B95" t="n">
-        <v>79685</v>
+        <v>78852</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9893,21 +9893,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>435156</v>
+        <v>435183</v>
       </c>
       <c r="R95" t="n">
-        <v>6782351</v>
+        <v>6782321</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9979,10 +9979,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129996337</v>
+        <v>129996230</v>
       </c>
       <c r="B96" t="n">
-        <v>78853</v>
+        <v>79714</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9990,21 +9990,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10014,10 +10014,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>435057</v>
+        <v>434674</v>
       </c>
       <c r="R96" t="n">
-        <v>6782494</v>
+        <v>6782596</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10044,12 +10044,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10076,10 +10076,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129996333</v>
+        <v>129996255</v>
       </c>
       <c r="B97" t="n">
-        <v>78853</v>
+        <v>79714</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10087,21 +10087,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10111,10 +10111,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>434909</v>
+        <v>434998</v>
       </c>
       <c r="R97" t="n">
-        <v>6782588</v>
+        <v>6782675</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10270,10 +10270,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129996282</v>
+        <v>129996457</v>
       </c>
       <c r="B99" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10281,21 +10281,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10305,10 +10305,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>435143</v>
+        <v>434993</v>
       </c>
       <c r="R99" t="n">
-        <v>6782302</v>
+        <v>6782408</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10367,10 +10367,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129996251</v>
+        <v>129996316</v>
       </c>
       <c r="B100" t="n">
-        <v>79714</v>
+        <v>57738</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10378,34 +10378,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>434956</v>
+        <v>434898</v>
       </c>
       <c r="R100" t="n">
-        <v>6782574</v>
+        <v>6782728</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10464,45 +10472,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129996237</v>
+        <v>129996355</v>
       </c>
       <c r="B101" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>434753</v>
+        <v>434841</v>
       </c>
       <c r="R101" t="n">
-        <v>6782550</v>
+        <v>6782494</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10543,6 +10560,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -10561,10 +10579,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129996257</v>
+        <v>129996338</v>
       </c>
       <c r="B102" t="n">
-        <v>79714</v>
+        <v>78853</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10572,21 +10590,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10596,10 +10614,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>435039</v>
+        <v>435074</v>
       </c>
       <c r="R102" t="n">
-        <v>6782675</v>
+        <v>6782438</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10658,10 +10676,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129996338</v>
+        <v>129996282</v>
       </c>
       <c r="B103" t="n">
-        <v>78853</v>
+        <v>79714</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10669,21 +10687,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10693,10 +10711,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>435074</v>
+        <v>435143</v>
       </c>
       <c r="R103" t="n">
-        <v>6782438</v>
+        <v>6782302</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10755,10 +10773,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129996316</v>
+        <v>129996249</v>
       </c>
       <c r="B104" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10766,42 +10784,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>434898</v>
+        <v>434946</v>
       </c>
       <c r="R104" t="n">
-        <v>6782728</v>
+        <v>6782584</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10860,10 +10870,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129996457</v>
+        <v>129996251</v>
       </c>
       <c r="B105" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10871,21 +10881,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10895,10 +10905,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>434993</v>
+        <v>434956</v>
       </c>
       <c r="R105" t="n">
-        <v>6782408</v>
+        <v>6782574</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10925,12 +10935,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10957,7 +10967,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129996249</v>
+        <v>129996237</v>
       </c>
       <c r="B106" t="n">
         <v>79714</v>
@@ -10992,10 +11002,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>434946</v>
+        <v>434753</v>
       </c>
       <c r="R106" t="n">
-        <v>6782584</v>
+        <v>6782550</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11054,54 +11064,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129996355</v>
+        <v>129996257</v>
       </c>
       <c r="B107" t="n">
-        <v>8451</v>
+        <v>79714</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>434841</v>
+        <v>435039</v>
       </c>
       <c r="R107" t="n">
-        <v>6782494</v>
+        <v>6782675</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11128,12 +11129,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11142,7 +11143,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11258,7 +11258,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129996242</v>
+        <v>129996276</v>
       </c>
       <c r="B109" t="n">
         <v>79714</v>
@@ -11293,10 +11293,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>434769</v>
+        <v>435207</v>
       </c>
       <c r="R109" t="n">
-        <v>6782593</v>
+        <v>6782192</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11323,12 +11323,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11355,7 +11355,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129996280</v>
+        <v>129996242</v>
       </c>
       <c r="B110" t="n">
         <v>79714</v>
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>435121</v>
+        <v>434769</v>
       </c>
       <c r="R110" t="n">
-        <v>6782201</v>
+        <v>6782593</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11420,12 +11420,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11452,10 +11452,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129996430</v>
+        <v>129996269</v>
       </c>
       <c r="B111" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11463,21 +11463,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11487,10 +11487,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>434828</v>
+        <v>435159</v>
       </c>
       <c r="R111" t="n">
-        <v>6782576</v>
+        <v>6782369</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11517,12 +11517,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11549,10 +11549,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129996448</v>
+        <v>129996280</v>
       </c>
       <c r="B112" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11560,21 +11560,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11584,10 +11584,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>435054</v>
+        <v>435121</v>
       </c>
       <c r="R112" t="n">
-        <v>6782627</v>
+        <v>6782201</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11743,10 +11743,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129996276</v>
+        <v>129996430</v>
       </c>
       <c r="B114" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11754,21 +11754,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11778,10 +11778,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>435207</v>
+        <v>434828</v>
       </c>
       <c r="R114" t="n">
-        <v>6782192</v>
+        <v>6782576</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11808,12 +11808,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11840,10 +11840,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129996269</v>
+        <v>129996448</v>
       </c>
       <c r="B115" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11851,21 +11851,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11875,10 +11875,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>435159</v>
+        <v>435054</v>
       </c>
       <c r="R115" t="n">
-        <v>6782369</v>
+        <v>6782627</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11937,27 +11937,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129996326</v>
+        <v>129996321</v>
       </c>
       <c r="B116" t="n">
-        <v>56934</v>
+        <v>57738</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -11970,7 +11970,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -11980,10 +11980,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>434930</v>
+        <v>434990</v>
       </c>
       <c r="R116" t="n">
-        <v>6782560</v>
+        <v>6782383</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12042,45 +12042,53 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129996291</v>
+        <v>129996326</v>
       </c>
       <c r="B117" t="n">
-        <v>79685</v>
+        <v>56934</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>102613</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>435034</v>
+        <v>434930</v>
       </c>
       <c r="R117" t="n">
-        <v>6782669</v>
+        <v>6782560</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12107,12 +12115,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12139,10 +12147,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129996321</v>
+        <v>129996291</v>
       </c>
       <c r="B118" t="n">
-        <v>57738</v>
+        <v>79685</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12150,42 +12158,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>434990</v>
+        <v>435034</v>
       </c>
       <c r="R118" t="n">
-        <v>6782383</v>
+        <v>6782669</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12244,45 +12244,48 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129996271</v>
+        <v>129996481</v>
       </c>
       <c r="B119" t="n">
-        <v>79714</v>
+        <v>92923</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>435189</v>
+        <v>434976</v>
       </c>
       <c r="R119" t="n">
-        <v>6782244</v>
+        <v>6782376</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12323,6 +12326,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12341,10 +12345,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129996259</v>
+        <v>129996447</v>
       </c>
       <c r="B120" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12352,21 +12356,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12376,10 +12380,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>435020</v>
+        <v>435039</v>
       </c>
       <c r="R120" t="n">
-        <v>6782612</v>
+        <v>6782658</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12438,7 +12442,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129996447</v>
+        <v>129996403</v>
       </c>
       <c r="B121" t="n">
         <v>79095</v>
@@ -12473,10 +12477,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>435039</v>
+        <v>435025</v>
       </c>
       <c r="R121" t="n">
-        <v>6782658</v>
+        <v>6782389</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12503,12 +12507,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12535,10 +12539,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129996403</v>
+        <v>129996271</v>
       </c>
       <c r="B122" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12546,21 +12550,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12570,10 +12574,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>435025</v>
+        <v>435189</v>
       </c>
       <c r="R122" t="n">
-        <v>6782389</v>
+        <v>6782244</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12600,12 +12604,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12632,48 +12636,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129996481</v>
+        <v>129996259</v>
       </c>
       <c r="B123" t="n">
-        <v>92921</v>
+        <v>79714</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>434976</v>
+        <v>435020</v>
       </c>
       <c r="R123" t="n">
-        <v>6782376</v>
+        <v>6782612</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12714,7 +12715,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13319,10 +13319,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129996476</v>
+        <v>129996240</v>
       </c>
       <c r="B130" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13330,21 +13330,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13354,10 +13354,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>435079</v>
+        <v>434765</v>
       </c>
       <c r="R130" t="n">
-        <v>6782284</v>
+        <v>6782566</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13384,17 +13384,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13421,10 +13416,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129996240</v>
+        <v>129996370</v>
       </c>
       <c r="B131" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13432,21 +13427,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13456,10 +13451,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>434765</v>
+        <v>434902</v>
       </c>
       <c r="R131" t="n">
-        <v>6782566</v>
+        <v>6782754</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13518,10 +13513,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129996370</v>
+        <v>129996238</v>
       </c>
       <c r="B132" t="n">
-        <v>78852</v>
+        <v>79714</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13529,21 +13524,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13553,10 +13548,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>434902</v>
+        <v>434763</v>
       </c>
       <c r="R132" t="n">
-        <v>6782754</v>
+        <v>6782555</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13615,7 +13610,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129996238</v>
+        <v>129996215</v>
       </c>
       <c r="B133" t="n">
         <v>79714</v>
@@ -13650,10 +13645,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>434763</v>
+        <v>434939</v>
       </c>
       <c r="R133" t="n">
-        <v>6782555</v>
+        <v>6782693</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13712,10 +13707,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129996215</v>
+        <v>129996476</v>
       </c>
       <c r="B134" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13723,21 +13718,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13747,10 +13742,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>434939</v>
+        <v>435079</v>
       </c>
       <c r="R134" t="n">
-        <v>6782693</v>
+        <v>6782284</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13777,12 +13772,17 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -13906,10 +13906,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129996239</v>
+        <v>129996453</v>
       </c>
       <c r="B136" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13917,21 +13917,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13941,10 +13941,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>434775</v>
+        <v>435011</v>
       </c>
       <c r="R136" t="n">
-        <v>6782566</v>
+        <v>6782456</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13971,12 +13971,17 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14003,7 +14008,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129996453</v>
+        <v>129996454</v>
       </c>
       <c r="B137" t="n">
         <v>79095</v>
@@ -14038,10 +14043,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>435011</v>
+        <v>435024</v>
       </c>
       <c r="R137" t="n">
-        <v>6782456</v>
+        <v>6782432</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14074,11 +14079,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14105,7 +14105,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129996270</v>
+        <v>129996266</v>
       </c>
       <c r="B138" t="n">
         <v>79714</v>
@@ -14140,10 +14140,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>435158</v>
+        <v>434994</v>
       </c>
       <c r="R138" t="n">
-        <v>6782353</v>
+        <v>6782358</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14202,10 +14202,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129996405</v>
+        <v>129996239</v>
       </c>
       <c r="B139" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14213,21 +14213,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14237,10 +14237,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>435097</v>
+        <v>434775</v>
       </c>
       <c r="R139" t="n">
-        <v>6782414</v>
+        <v>6782566</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14299,10 +14299,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129996388</v>
+        <v>129996270</v>
       </c>
       <c r="B140" t="n">
-        <v>78852</v>
+        <v>79714</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14310,21 +14310,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14334,10 +14334,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>435210</v>
+        <v>435158</v>
       </c>
       <c r="R140" t="n">
-        <v>6782209</v>
+        <v>6782353</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14396,10 +14396,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129996369</v>
+        <v>129996405</v>
       </c>
       <c r="B141" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14407,21 +14407,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14431,10 +14431,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>434939</v>
+        <v>435097</v>
       </c>
       <c r="R141" t="n">
-        <v>6782721</v>
+        <v>6782414</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14493,10 +14493,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129996454</v>
+        <v>129996388</v>
       </c>
       <c r="B142" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14504,21 +14504,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14528,10 +14528,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>435024</v>
+        <v>435210</v>
       </c>
       <c r="R142" t="n">
-        <v>6782432</v>
+        <v>6782209</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14590,10 +14590,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129996266</v>
+        <v>129996369</v>
       </c>
       <c r="B143" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14601,21 +14601,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14625,10 +14625,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>434994</v>
+        <v>434939</v>
       </c>
       <c r="R143" t="n">
-        <v>6782358</v>
+        <v>6782721</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14655,12 +14655,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14687,10 +14687,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129996243</v>
+        <v>129996458</v>
       </c>
       <c r="B144" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14698,21 +14698,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14722,10 +14722,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>434780</v>
+        <v>434987</v>
       </c>
       <c r="R144" t="n">
-        <v>6782593</v>
+        <v>6782372</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14752,12 +14752,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -14784,10 +14784,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129996381</v>
+        <v>129996412</v>
       </c>
       <c r="B145" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14795,34 +14795,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>434974</v>
+        <v>434847</v>
       </c>
       <c r="R145" t="n">
-        <v>6782389</v>
+        <v>6782878</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14849,12 +14852,17 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -14863,6 +14871,7 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -14881,10 +14890,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129996317</v>
+        <v>129996460</v>
       </c>
       <c r="B146" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14892,42 +14901,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>434837</v>
+        <v>435106</v>
       </c>
       <c r="R146" t="n">
-        <v>6782880</v>
+        <v>6782315</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14954,12 +14955,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -14986,10 +14987,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129996289</v>
+        <v>129996411</v>
       </c>
       <c r="B147" t="n">
-        <v>79685</v>
+        <v>79095</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14997,21 +14998,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15021,10 +15022,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>434909</v>
+        <v>434854</v>
       </c>
       <c r="R147" t="n">
-        <v>6782588</v>
+        <v>6782808</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15083,10 +15084,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129996458</v>
+        <v>129996243</v>
       </c>
       <c r="B148" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15094,21 +15095,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15118,10 +15119,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>434987</v>
+        <v>434780</v>
       </c>
       <c r="R148" t="n">
-        <v>6782372</v>
+        <v>6782593</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15148,12 +15149,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15180,10 +15181,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129996412</v>
+        <v>129996381</v>
       </c>
       <c r="B149" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15191,37 +15192,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>434847</v>
+        <v>434974</v>
       </c>
       <c r="R149" t="n">
-        <v>6782878</v>
+        <v>6782389</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15248,17 +15246,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15267,7 +15260,6 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15286,10 +15278,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129996460</v>
+        <v>129996317</v>
       </c>
       <c r="B150" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15297,34 +15289,42 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>435106</v>
+        <v>434837</v>
       </c>
       <c r="R150" t="n">
-        <v>6782315</v>
+        <v>6782880</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15351,12 +15351,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15383,45 +15383,54 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129996411</v>
+        <v>129996361</v>
       </c>
       <c r="B151" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>434854</v>
+        <v>435003</v>
       </c>
       <c r="R151" t="n">
-        <v>6782808</v>
+        <v>6782399</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15448,12 +15457,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15462,6 +15471,7 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -15480,54 +15490,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129996361</v>
+        <v>129996289</v>
       </c>
       <c r="B152" t="n">
-        <v>8451</v>
+        <v>79685</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>435003</v>
+        <v>434909</v>
       </c>
       <c r="R152" t="n">
-        <v>6782399</v>
+        <v>6782588</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15554,12 +15555,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15568,7 +15569,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -15587,10 +15587,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129996312</v>
+        <v>129996225</v>
       </c>
       <c r="B153" t="n">
-        <v>57900</v>
+        <v>79714</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15598,42 +15598,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>435077</v>
+        <v>434627</v>
       </c>
       <c r="R153" t="n">
-        <v>6782299</v>
+        <v>6782646</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15660,12 +15652,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -15692,7 +15684,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129996225</v>
+        <v>129996278</v>
       </c>
       <c r="B154" t="n">
         <v>79714</v>
@@ -15727,10 +15719,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>434627</v>
+        <v>435146</v>
       </c>
       <c r="R154" t="n">
-        <v>6782646</v>
+        <v>6782198</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15757,12 +15749,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -15789,10 +15781,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129996278</v>
+        <v>129996372</v>
       </c>
       <c r="B155" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15800,21 +15792,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15824,10 +15816,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>435146</v>
+        <v>434761</v>
       </c>
       <c r="R155" t="n">
-        <v>6782198</v>
+        <v>6782557</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -15854,12 +15846,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -15886,10 +15878,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129996452</v>
+        <v>129996256</v>
       </c>
       <c r="B156" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15897,21 +15889,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15921,10 +15913,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>435052</v>
+        <v>435012</v>
       </c>
       <c r="R156" t="n">
-        <v>6782442</v>
+        <v>6782696</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -15957,11 +15949,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -15988,10 +15975,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129996372</v>
+        <v>129996452</v>
       </c>
       <c r="B157" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15999,21 +15986,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16023,10 +16010,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>434761</v>
+        <v>435052</v>
       </c>
       <c r="R157" t="n">
-        <v>6782557</v>
+        <v>6782442</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16053,12 +16040,17 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16085,10 +16077,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129996256</v>
+        <v>129996470</v>
       </c>
       <c r="B158" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16096,21 +16088,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16120,10 +16112,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>435012</v>
+        <v>435154</v>
       </c>
       <c r="R158" t="n">
-        <v>6782696</v>
+        <v>6782190</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16182,7 +16174,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129996475</v>
+        <v>129996440</v>
       </c>
       <c r="B159" t="n">
         <v>79095</v>
@@ -16217,10 +16209,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>435086</v>
+        <v>434996</v>
       </c>
       <c r="R159" t="n">
-        <v>6782263</v>
+        <v>6782623</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16279,53 +16271,45 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129996304</v>
+        <v>129996475</v>
       </c>
       <c r="B160" t="n">
-        <v>56931</v>
+        <v>79095</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>435028</v>
+        <v>435086</v>
       </c>
       <c r="R160" t="n">
-        <v>6782608</v>
+        <v>6782263</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16384,45 +16368,53 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129996470</v>
+        <v>129996304</v>
       </c>
       <c r="B161" t="n">
-        <v>79095</v>
+        <v>56931</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>435154</v>
+        <v>435028</v>
       </c>
       <c r="R161" t="n">
-        <v>6782190</v>
+        <v>6782608</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16481,10 +16473,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129996440</v>
+        <v>129996312</v>
       </c>
       <c r="B162" t="n">
-        <v>79095</v>
+        <v>57900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16492,34 +16484,42 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>434996</v>
+        <v>435077</v>
       </c>
       <c r="R162" t="n">
-        <v>6782623</v>
+        <v>6782299</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16772,10 +16772,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129996236</v>
+        <v>129996409</v>
       </c>
       <c r="B165" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16783,21 +16783,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -16807,10 +16807,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>434744</v>
+        <v>434902</v>
       </c>
       <c r="R165" t="n">
-        <v>6782553</v>
+        <v>6782760</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -16869,10 +16869,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129996343</v>
+        <v>129996433</v>
       </c>
       <c r="B166" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16880,21 +16880,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -16904,10 +16904,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>435133</v>
+        <v>434947</v>
       </c>
       <c r="R166" t="n">
-        <v>6782359</v>
+        <v>6782576</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -16934,12 +16934,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17063,10 +17063,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129996409</v>
+        <v>129996236</v>
       </c>
       <c r="B168" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17074,21 +17074,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17098,10 +17098,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>434902</v>
+        <v>434744</v>
       </c>
       <c r="R168" t="n">
-        <v>6782760</v>
+        <v>6782553</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17160,10 +17160,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129996262</v>
+        <v>129996417</v>
       </c>
       <c r="B169" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17171,21 +17171,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17195,10 +17195,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>435074</v>
+        <v>434721</v>
       </c>
       <c r="R169" t="n">
-        <v>6782543</v>
+        <v>6782708</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17225,12 +17225,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17257,10 +17257,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129996379</v>
+        <v>129996262</v>
       </c>
       <c r="B170" t="n">
-        <v>78852</v>
+        <v>79714</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17268,21 +17268,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17292,10 +17292,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>435059</v>
+        <v>435074</v>
       </c>
       <c r="R170" t="n">
-        <v>6782496</v>
+        <v>6782543</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17354,7 +17354,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129996390</v>
+        <v>129996379</v>
       </c>
       <c r="B171" t="n">
         <v>78852</v>
@@ -17389,10 +17389,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>435126</v>
+        <v>435059</v>
       </c>
       <c r="R171" t="n">
-        <v>6782191</v>
+        <v>6782496</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17451,10 +17451,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129996258</v>
+        <v>129996390</v>
       </c>
       <c r="B172" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17462,21 +17462,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17486,10 +17486,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>435024</v>
+        <v>435126</v>
       </c>
       <c r="R172" t="n">
-        <v>6782675</v>
+        <v>6782191</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17548,10 +17548,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129996417</v>
+        <v>129996258</v>
       </c>
       <c r="B173" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17559,21 +17559,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17583,10 +17583,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>434721</v>
+        <v>435024</v>
       </c>
       <c r="R173" t="n">
-        <v>6782708</v>
+        <v>6782675</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17613,12 +17613,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -17645,10 +17645,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129996433</v>
+        <v>129996343</v>
       </c>
       <c r="B174" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17656,21 +17656,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17680,10 +17680,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>434947</v>
+        <v>435133</v>
       </c>
       <c r="R174" t="n">
-        <v>6782576</v>
+        <v>6782359</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17710,12 +17710,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -17849,10 +17849,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129996245</v>
+        <v>129996345</v>
       </c>
       <c r="B176" t="n">
-        <v>79714</v>
+        <v>78853</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17860,21 +17860,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -17884,10 +17884,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>434796</v>
+        <v>435178</v>
       </c>
       <c r="R176" t="n">
-        <v>6782579</v>
+        <v>6782321</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -17914,12 +17914,12 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -17946,10 +17946,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129996382</v>
+        <v>129996341</v>
       </c>
       <c r="B177" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17957,21 +17957,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -17981,10 +17981,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>434962</v>
+        <v>434996</v>
       </c>
       <c r="R177" t="n">
-        <v>6782388</v>
+        <v>6782360</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18043,7 +18043,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129996220</v>
+        <v>129996245</v>
       </c>
       <c r="B178" t="n">
         <v>79714</v>
@@ -18078,10 +18078,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>434883</v>
+        <v>434796</v>
       </c>
       <c r="R178" t="n">
-        <v>6782700</v>
+        <v>6782579</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18140,10 +18140,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129996414</v>
+        <v>129996382</v>
       </c>
       <c r="B179" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18151,21 +18151,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18175,10 +18175,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>434827</v>
+        <v>434962</v>
       </c>
       <c r="R179" t="n">
-        <v>6782863</v>
+        <v>6782388</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18205,12 +18205,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -18237,7 +18237,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129996254</v>
+        <v>129996220</v>
       </c>
       <c r="B180" t="n">
         <v>79714</v>
@@ -18272,10 +18272,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>434995</v>
+        <v>434883</v>
       </c>
       <c r="R180" t="n">
-        <v>6782672</v>
+        <v>6782700</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18302,12 +18302,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -18334,7 +18334,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129996418</v>
+        <v>129996414</v>
       </c>
       <c r="B181" t="n">
         <v>79095</v>
@@ -18363,19 +18363,16 @@
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>434692</v>
+        <v>434827</v>
       </c>
       <c r="R181" t="n">
-        <v>6782718</v>
+        <v>6782863</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18410,18 +18407,12 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
-        </is>
-      </c>
       <c r="AD181" t="b">
         <v>0</v>
       </c>
       <c r="AE181" t="b">
         <v>0</v>
       </c>
-      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
       </c>
@@ -18440,10 +18431,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129996345</v>
+        <v>129996254</v>
       </c>
       <c r="B182" t="n">
-        <v>78853</v>
+        <v>79714</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18451,21 +18442,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18475,10 +18466,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>435178</v>
+        <v>434995</v>
       </c>
       <c r="R182" t="n">
-        <v>6782321</v>
+        <v>6782672</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18537,10 +18528,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129996341</v>
+        <v>129996418</v>
       </c>
       <c r="B183" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18548,34 +18539,37 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>434996</v>
+        <v>434692</v>
       </c>
       <c r="R183" t="n">
-        <v>6782360</v>
+        <v>6782718</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18602,12 +18596,17 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -18616,6 +18615,7 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
@@ -18634,10 +18634,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129996429</v>
+        <v>129996322</v>
       </c>
       <c r="B184" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18645,34 +18645,42 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>434796</v>
+        <v>434994</v>
       </c>
       <c r="R184" t="n">
-        <v>6782586</v>
+        <v>6782340</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18699,17 +18707,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -18736,7 +18739,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129996467</v>
+        <v>129996429</v>
       </c>
       <c r="B185" t="n">
         <v>79095</v>
@@ -18771,10 +18774,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>435205</v>
+        <v>434796</v>
       </c>
       <c r="R185" t="n">
-        <v>6782175</v>
+        <v>6782586</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -18801,12 +18804,17 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -18833,7 +18841,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129996273</v>
+        <v>129996252</v>
       </c>
       <c r="B186" t="n">
         <v>79714</v>
@@ -18868,10 +18876,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>435238</v>
+        <v>435114</v>
       </c>
       <c r="R186" t="n">
-        <v>6782244</v>
+        <v>6782479</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18930,10 +18938,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129996235</v>
+        <v>129996467</v>
       </c>
       <c r="B187" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18941,21 +18949,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -18965,10 +18973,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>434763</v>
+        <v>435205</v>
       </c>
       <c r="R187" t="n">
-        <v>6782543</v>
+        <v>6782175</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -18995,12 +19003,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19027,10 +19035,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129996322</v>
+        <v>129996277</v>
       </c>
       <c r="B188" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19038,42 +19046,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>434994</v>
+        <v>435153</v>
       </c>
       <c r="R188" t="n">
-        <v>6782340</v>
+        <v>6782169</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19132,7 +19132,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129996252</v>
+        <v>129996273</v>
       </c>
       <c r="B189" t="n">
         <v>79714</v>
@@ -19167,10 +19167,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>435114</v>
+        <v>435238</v>
       </c>
       <c r="R189" t="n">
-        <v>6782479</v>
+        <v>6782244</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19229,7 +19229,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129996277</v>
+        <v>129996235</v>
       </c>
       <c r="B190" t="n">
         <v>79714</v>
@@ -19264,10 +19264,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>435153</v>
+        <v>434763</v>
       </c>
       <c r="R190" t="n">
-        <v>6782169</v>
+        <v>6782543</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19294,12 +19294,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -19621,10 +19621,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129996376</v>
+        <v>129996425</v>
       </c>
       <c r="B194" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19632,21 +19632,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19656,10 +19656,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>435039</v>
+        <v>434836</v>
       </c>
       <c r="R194" t="n">
-        <v>6782675</v>
+        <v>6782524</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19686,12 +19686,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -19718,10 +19718,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129996263</v>
+        <v>129996376</v>
       </c>
       <c r="B195" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19729,21 +19729,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -19753,10 +19753,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>435076</v>
+        <v>435039</v>
       </c>
       <c r="R195" t="n">
-        <v>6782532</v>
+        <v>6782675</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -19815,10 +19815,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129996425</v>
+        <v>129996263</v>
       </c>
       <c r="B196" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19826,21 +19826,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -19850,10 +19850,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>434836</v>
+        <v>435076</v>
       </c>
       <c r="R196" t="n">
-        <v>6782524</v>
+        <v>6782532</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -19880,12 +19880,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -19912,7 +19912,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129996268</v>
+        <v>129996244</v>
       </c>
       <c r="B197" t="n">
         <v>79714</v>
@@ -19947,10 +19947,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>435103</v>
+        <v>434789</v>
       </c>
       <c r="R197" t="n">
-        <v>6782305</v>
+        <v>6782590</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -19977,12 +19977,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20009,7 +20009,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129996244</v>
+        <v>129996268</v>
       </c>
       <c r="B198" t="n">
         <v>79714</v>
@@ -20044,10 +20044,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>434789</v>
+        <v>435103</v>
       </c>
       <c r="R198" t="n">
-        <v>6782590</v>
+        <v>6782305</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20074,12 +20074,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -20203,45 +20203,54 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129996219</v>
+        <v>129996364</v>
       </c>
       <c r="B200" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>434922</v>
+        <v>435098</v>
       </c>
       <c r="R200" t="n">
-        <v>6782675</v>
+        <v>6782306</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20268,12 +20277,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -20282,6 +20291,7 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
+      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -20300,10 +20310,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129996272</v>
+        <v>129996471</v>
       </c>
       <c r="B201" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20311,21 +20321,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20335,10 +20345,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>435213</v>
+        <v>435126</v>
       </c>
       <c r="R201" t="n">
-        <v>6782257</v>
+        <v>6782203</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20397,10 +20407,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129996325</v>
+        <v>129996219</v>
       </c>
       <c r="B202" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20408,42 +20418,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>434755</v>
+        <v>434922</v>
       </c>
       <c r="R202" t="n">
-        <v>6782589</v>
+        <v>6782675</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20502,10 +20504,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129996471</v>
+        <v>129996272</v>
       </c>
       <c r="B203" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20513,21 +20515,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20537,10 +20539,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>435126</v>
+        <v>435213</v>
       </c>
       <c r="R203" t="n">
-        <v>6782203</v>
+        <v>6782257</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20599,10 +20601,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129996330</v>
+        <v>129996325</v>
       </c>
       <c r="B204" t="n">
-        <v>78853</v>
+        <v>57738</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20610,34 +20612,42 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>434763</v>
+        <v>434755</v>
       </c>
       <c r="R204" t="n">
-        <v>6782555</v>
+        <v>6782589</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20696,54 +20706,45 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129996364</v>
+        <v>129996330</v>
       </c>
       <c r="B205" t="n">
-        <v>8451</v>
+        <v>78853</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Stor-Uppdjusen, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>435098</v>
+        <v>434763</v>
       </c>
       <c r="R205" t="n">
-        <v>6782306</v>
+        <v>6782555</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -20770,12 +20771,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -20784,7 +20785,6 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
-      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59104-2025 artfynd.xlsx
+++ b/artfynd/A 59104-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY238"/>
+  <dimension ref="A1:AZ238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134041442</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996479</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996480</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996481</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996482</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1305,6 +1335,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996213</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996403</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1499,6 +1539,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996404</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996405</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1693,6 +1743,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996406</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1790,6 +1845,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996407</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1887,6 +1947,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996408</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1984,6 +2049,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996409</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996410</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2183,6 +2258,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996411</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2289,6 +2369,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996412</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2386,6 +2471,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996413</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2483,6 +2573,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996414</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2585,6 +2680,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996415</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2682,6 +2782,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996417</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2788,6 +2893,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996418</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2885,6 +2995,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996419</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2982,6 +3097,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996420</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3079,6 +3199,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996421</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3176,6 +3301,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996422</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3273,6 +3403,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996423</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3370,6 +3505,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996424</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3467,6 +3607,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996425</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3564,6 +3709,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996426</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3661,6 +3811,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996427</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3763,6 +3918,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996429</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3860,6 +4020,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996430</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3957,6 +4122,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996431</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4059,6 +4229,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996432</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4156,6 +4331,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996433</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4253,6 +4433,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996434</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4350,6 +4535,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996435</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4452,6 +4642,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996436</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4549,6 +4744,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996437</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4646,6 +4846,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996438</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4743,6 +4948,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996439</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4840,6 +5050,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996440</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4937,6 +5152,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996441</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5034,6 +5254,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996444</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5131,6 +5356,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996445</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5228,6 +5458,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996446</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5325,6 +5560,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996447</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5422,6 +5662,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996448</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5519,6 +5764,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996449</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5625,6 +5875,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996450</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5727,6 +5982,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996451</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5829,6 +6089,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996452</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5931,6 +6196,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996453</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6028,6 +6298,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996454</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6125,6 +6400,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996455</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6222,6 +6502,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996456</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6319,6 +6604,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996457</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6416,6 +6706,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996458</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6513,6 +6808,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996459</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6610,6 +6910,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996460</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6712,6 +7017,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996461</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6809,6 +7119,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996462</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6906,6 +7221,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996463</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7007,6 +7327,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996464</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7109,6 +7434,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996465</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7206,6 +7536,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996466</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7303,6 +7638,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996467</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7400,6 +7740,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996468</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7497,6 +7842,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996470</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7594,6 +7944,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996471</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7691,6 +8046,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996472</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7788,6 +8148,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996473</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7885,6 +8250,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996474</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7982,6 +8352,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996475</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8084,6 +8459,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996476</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8181,6 +8561,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996477</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8287,6 +8672,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996478</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8403,6 +8793,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134041441</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8519,6 +8914,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134041443</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8616,6 +9016,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996369</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8713,6 +9118,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996370</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8810,6 +9220,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996371</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8907,6 +9322,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996372</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9004,6 +9424,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996374</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9101,6 +9526,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996375</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9198,6 +9628,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996376</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9295,6 +9730,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996377</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9392,6 +9832,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996378</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9489,6 +9934,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996379</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9586,6 +10036,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996380</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9683,6 +10138,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996381</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9780,6 +10240,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996382</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9877,6 +10342,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996383</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9974,6 +10444,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996385</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10071,6 +10546,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996387</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10168,6 +10648,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996388</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10265,6 +10750,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996390</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10362,6 +10852,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996214</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10459,6 +10954,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996215</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10556,6 +11056,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996216</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10653,6 +11158,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996217</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10750,6 +11260,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996218</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10847,6 +11362,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996219</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10944,6 +11464,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996220</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11041,6 +11566,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996221</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11138,6 +11668,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996222</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11235,6 +11770,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996223</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11332,6 +11872,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996224</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11429,6 +11974,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996225</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11526,6 +12076,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996226</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11623,6 +12178,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996227</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11720,6 +12280,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996229</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11817,6 +12382,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996230</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11914,6 +12484,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996231</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12011,6 +12586,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996232</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12108,6 +12688,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996234</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12205,6 +12790,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996235</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12302,6 +12892,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996236</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12399,6 +12994,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996237</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12496,6 +13096,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996238</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12593,6 +13198,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996239</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12690,6 +13300,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996240</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12787,6 +13402,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996241</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12884,6 +13504,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996242</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12981,6 +13606,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996243</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13078,6 +13708,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996244</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13175,6 +13810,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996245</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13272,6 +13912,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996246</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13369,6 +14014,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996247</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13466,6 +14116,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996248</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13563,6 +14218,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996249</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13660,6 +14320,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996250</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13757,6 +14422,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996251</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13854,6 +14524,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996252</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13951,6 +14626,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996253</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14048,6 +14728,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996254</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14145,6 +14830,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996255</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14242,6 +14932,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996256</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14339,6 +15034,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996257</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14436,6 +15136,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996258</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14533,6 +15238,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996259</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14630,6 +15340,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996260</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14727,6 +15442,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996262</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14824,6 +15544,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996263</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14921,6 +15646,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996264</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15018,6 +15748,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996265</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15115,6 +15850,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996266</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15212,6 +15952,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996267</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15309,6 +16054,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996268</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15406,6 +16156,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996269</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15503,6 +16258,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996270</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15600,6 +16360,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996271</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15697,6 +16462,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996272</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15794,6 +16564,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996273</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -15891,6 +16666,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996274</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -15988,6 +16768,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996275</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16085,6 +16870,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996276</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16182,6 +16972,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996277</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16279,6 +17074,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996278</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16376,6 +17176,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996279</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16473,6 +17278,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996280</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16570,6 +17380,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996281</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16667,6 +17482,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996282</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16764,6 +17584,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996283</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -16861,6 +17686,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996483</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -16966,6 +17796,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996316</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17071,6 +17906,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996317</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17176,6 +18016,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996319</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17281,6 +18126,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996320</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17386,6 +18236,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996321</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17491,6 +18346,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996322</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17596,6 +18456,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996323</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17701,6 +18566,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996324</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -17806,6 +18676,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996325</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -17911,6 +18786,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996303</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18016,6 +18896,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996304</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18121,6 +19006,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996305</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18226,6 +19116,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996326</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18331,6 +19226,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996309</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18436,6 +19336,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996310</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18541,6 +19446,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996311</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18646,6 +19556,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996312</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18753,6 +19668,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996353</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18860,6 +19780,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996354</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -18967,6 +19892,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996355</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19074,6 +20004,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996356</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19181,6 +20116,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996357</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19288,6 +20228,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996358</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19395,6 +20340,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996359</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19502,6 +20452,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996360</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19609,6 +20564,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996361</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19716,6 +20676,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996362</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19823,6 +20788,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996363</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -19930,6 +20900,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996364</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20037,6 +21012,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996365</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20144,6 +21124,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996366</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20245,6 +21230,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996327</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20342,6 +21332,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996328</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20439,6 +21434,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996329</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20536,6 +21536,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996330</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20633,6 +21638,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996331</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20730,6 +21740,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996332</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -20827,6 +21842,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996333</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -20928,6 +21948,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996334</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21025,6 +22050,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996335</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21122,6 +22152,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996336</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21219,6 +22254,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996337</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21316,6 +22356,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996338</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21413,6 +22458,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996339</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21510,6 +22560,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996340</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21607,6 +22662,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996341</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21704,6 +22764,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996342</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -21801,6 +22866,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996343</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -21898,6 +22968,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996344</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -21995,6 +23070,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996345</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22092,6 +23172,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996346</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22189,6 +23274,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996347</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22286,6 +23376,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996348</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22383,6 +23478,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996349</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22480,6 +23580,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996350</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22577,6 +23682,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996351</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22674,6 +23784,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996352</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -22771,6 +23886,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996284</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -22868,6 +23988,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996285</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -22965,6 +24090,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996286</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23062,6 +24192,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996288</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -23159,6 +24294,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996289</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23256,6 +24396,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996290</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23353,6 +24498,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996291</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23450,6 +24600,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996292</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -23547,6 +24702,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996293</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -23644,6 +24804,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996294</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -23741,6 +24906,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996295</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -23838,6 +25008,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996296</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -23935,6 +25110,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996297</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -24032,6 +25212,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996298</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -24129,8 +25314,252 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996299</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>